--- a/assets/FinSight_IA_Template_REIT_v1.xlsx
+++ b/assets/FinSight_IA_Template_REIT_v1.xlsx
@@ -16176,7 +16176,7 @@
       </c>
       <c r="B7" s="427" t="inlineStr">
         <is>
-          <t>VALUATION RATIOS — OIL &amp; GAS</t>
+          <t>RATIOS DE VALORISATION — REIT</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -16200,7 +16200,7 @@
       <c r="A9" s="182" t="n"/>
       <c r="B9" s="422" t="inlineStr">
         <is>
-          <t>EV / DACF (Debt-Adjusted Cash Flow)</t>
+          <t>P/FFO (Price / Funds From Ops)</t>
         </is>
       </c>
       <c r="C9" s="417" t="n"/>
@@ -16225,7 +16225,7 @@
         </is>
       </c>
       <c r="H9" s="547">
-        <f>IFERROR(INPUT!H98/(INPUT!H75+ABS(INPUT!H20)*(1-INPUT!H104)),"–")</f>
+        <f>IFERROR(INPUT!H97/(INPUT!H26+ABS(INPUT!H16)),"–")</f>
         <v/>
       </c>
     </row>
@@ -16233,7 +16233,7 @@
       <c r="A10" s="182" t="n"/>
       <c r="B10" s="422" t="inlineStr">
         <is>
-          <t>EV / EBITDAX</t>
+          <t>P/AFFO (Price / Adj. FFO)</t>
         </is>
       </c>
       <c r="C10" s="417" t="n"/>
@@ -16258,7 +16258,7 @@
         </is>
       </c>
       <c r="H10" s="547">
-        <f>IFERROR(INPUT!H98/(INPUT!H30+ABS(INPUT!H15)),"–")</f>
+        <f>IFERROR(INPUT!H97/(INPUT!H26+ABS(INPUT!H16)-ABS(INPUT!H78)),"–")</f>
         <v/>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
       <c r="A13" s="182" t="n"/>
       <c r="B13" s="422" t="inlineStr">
         <is>
-          <t>EV / Production ($/BOE/d)</t>
+          <t>P/NAV (Price / Net Asset Value)</t>
         </is>
       </c>
       <c r="C13" s="417" t="n"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="H13" s="549" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>n.d. — source expert</t>
         </is>
       </c>
     </row>
@@ -16366,7 +16366,7 @@
       <c r="A14" s="182" t="n"/>
       <c r="B14" s="422" t="inlineStr">
         <is>
-          <t>Price / Reserves 1P (EV/BOE)</t>
+          <t>Cap Rate</t>
         </is>
       </c>
       <c r="C14" s="417" t="n"/>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="H14" s="549" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>n.d. — source expert</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16497,7 @@
       <c r="A20" s="182" t="n"/>
       <c r="B20" s="66" t="inlineStr">
         <is>
-          <t>EBITDAX Margin</t>
+          <t>EBITDA Margin (NOI proxy)</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
@@ -17389,7 +17389,7 @@
       <c r="A58" s="182" t="n"/>
       <c r="B58" s="415" t="inlineStr">
         <is>
-          <t>OIL &amp; GAS OPERATIONAL METRICS</t>
+          <t>MÉTRIQUES OPÉRATIONNELLES — REIT</t>
         </is>
       </c>
       <c r="C58" s="454" t="n"/>
@@ -17413,104 +17413,120 @@
       <c r="A60" s="182" t="n"/>
       <c r="B60" s="416" t="inlineStr">
         <is>
-          <t>Net Debt / EBITDAX</t>
+          <t>FFO / Share</t>
         </is>
       </c>
       <c r="C60" s="417" t="n"/>
       <c r="D60" s="526" t="n"/>
-      <c r="E60" s="558">
-        <f>IFERROR((INPUT!E49+INPUT!E55-INPUT!E34)/(INPUT!E30+ABS(INPUT!E15)),"–")</f>
-        <v/>
-      </c>
-      <c r="F60" s="558">
-        <f>IFERROR((INPUT!F49+INPUT!F55-INPUT!F34)/(INPUT!F30+ABS(INPUT!F15)),"–")</f>
-        <v/>
-      </c>
-      <c r="G60" s="558">
-        <f>IFERROR((INPUT!G49+INPUT!G55-INPUT!G34)/(INPUT!G30+ABS(INPUT!G15)),"–")</f>
-        <v/>
-      </c>
-      <c r="H60" s="559">
-        <f>IFERROR((INPUT!H49+INPUT!H55-INPUT!H34)/(INPUT!H30+ABS(INPUT!H15)),"–")</f>
-        <v/>
+      <c r="E60" s="558" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F60" s="558" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G60" s="558" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="H60" s="559" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="489">
       <c r="A61" s="182" t="n"/>
       <c r="B61" s="416" t="inlineStr">
         <is>
-          <t>CapEx / DD&amp;A (Reinvestment Rate)</t>
+          <t>AFFO / Share</t>
         </is>
       </c>
       <c r="C61" s="417" t="n"/>
       <c r="D61" s="526" t="n"/>
-      <c r="E61" s="558">
-        <f>IFERROR(ABS(INPUT!E78)/ABS(INPUT!E16),"–")</f>
-        <v/>
-      </c>
-      <c r="F61" s="558">
-        <f>IFERROR(ABS(INPUT!F78)/ABS(INPUT!F16),"–")</f>
-        <v/>
-      </c>
-      <c r="G61" s="558">
-        <f>IFERROR(ABS(INPUT!G78)/ABS(INPUT!G16),"–")</f>
-        <v/>
-      </c>
-      <c r="H61" s="559">
-        <f>IFERROR(ABS(INPUT!H78)/ABS(INPUT!H16),"–")</f>
-        <v/>
+      <c r="E61" s="558" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F61" s="558" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G61" s="558" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="H61" s="559" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="489">
       <c r="A62" s="182" t="n"/>
       <c r="B62" s="416" t="inlineStr">
         <is>
-          <t>DACF (Debt-Adjusted Cash Flow, $M)</t>
+          <t>LTV Ratio</t>
         </is>
       </c>
       <c r="C62" s="417" t="n"/>
       <c r="D62" s="526" t="n"/>
-      <c r="E62" s="419">
-        <f>IFERROR(INPUT!E75+ABS(INPUT!E20)*(1-INPUT!E104),"–")</f>
-        <v/>
-      </c>
-      <c r="F62" s="419">
-        <f>IFERROR(INPUT!F75+ABS(INPUT!F20)*(1-INPUT!F104),"–")</f>
-        <v/>
-      </c>
-      <c r="G62" s="419">
-        <f>IFERROR(INPUT!G75+ABS(INPUT!G20)*(1-INPUT!G104),"–")</f>
-        <v/>
-      </c>
-      <c r="H62" s="457">
-        <f>IFERROR(INPUT!H75+ABS(INPUT!H20)*(1-INPUT!H104),"–")</f>
-        <v/>
+      <c r="E62" s="419" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F62" s="419" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G62" s="419" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="H62" s="457" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="489">
       <c r="A63" s="182" t="n"/>
       <c r="B63" s="416" t="inlineStr">
         <is>
-          <t>EBITDAX ($M)</t>
+          <t>Occupancy Rate (n.d.)</t>
         </is>
       </c>
       <c r="C63" s="417" t="n"/>
       <c r="D63" s="526" t="n"/>
-      <c r="E63" s="419">
-        <f>IFERROR(INPUT!E30+ABS(INPUT!E15),"–")</f>
-        <v/>
-      </c>
-      <c r="F63" s="419">
-        <f>IFERROR(INPUT!F30+ABS(INPUT!F15),"–")</f>
-        <v/>
-      </c>
-      <c r="G63" s="419">
-        <f>IFERROR(INPUT!G30+ABS(INPUT!G15),"–")</f>
-        <v/>
-      </c>
-      <c r="H63" s="457">
-        <f>IFERROR(INPUT!H30+ABS(INPUT!H15),"–")</f>
-        <v/>
+      <c r="E63" s="419" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="F63" s="419" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="G63" s="419" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
+      </c>
+      <c r="H63" s="457" t="inlineStr">
+        <is>
+          <t>n.d.</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="489">
@@ -19631,7 +19647,7 @@
       <c r="A40" s="462" t="n"/>
       <c r="B40" s="462" t="inlineStr">
         <is>
-          <t>OIL PRICE DECK &amp; REVENUE SENSITIVITY</t>
+          <t>(Section Brent désactivée — non pertinente REIT)</t>
         </is>
       </c>
       <c r="C40" s="462" t="n"/>
@@ -19649,46 +19665,18 @@
     </row>
     <row r="41" ht="18" customHeight="1" s="489" thickBot="1">
       <c r="A41" s="474" t="n"/>
-      <c r="B41" s="69" t="inlineStr">
-        <is>
-          <t>Brent Crude — Bear / Base / Bull ($/bbl)</t>
-        </is>
-      </c>
+      <c r="B41" s="69" t="n"/>
       <c r="C41" s="191" t="n"/>
-      <c r="D41" s="471" t="inlineStr">
-        <is>
-          <t>Bear ($60)</t>
-        </is>
-      </c>
-      <c r="E41" s="471" t="inlineStr">
-        <is>
-          <t>Base ($75)</t>
-        </is>
-      </c>
-      <c r="F41" s="471" t="inlineStr">
-        <is>
-          <t>Bull ($90)</t>
-        </is>
-      </c>
-      <c r="G41" s="463" t="inlineStr">
-        <is>
-          <t>Bear  |  Base  |  Bull</t>
-        </is>
-      </c>
+      <c r="D41" s="471" t="n"/>
+      <c r="E41" s="471" t="n"/>
+      <c r="F41" s="471" t="n"/>
+      <c r="G41" s="463" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1" s="489" thickBot="1">
       <c r="A42" s="107" t="n"/>
-      <c r="B42" s="504" t="inlineStr">
-        <is>
-          <t>Active Brent Price ($/bbl) — change here</t>
-        </is>
-      </c>
+      <c r="B42" s="504" t="n"/>
       <c r="C42" s="417" t="n"/>
-      <c r="D42" s="473" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
+      <c r="D42" s="473" t="n"/>
       <c r="E42" s="472">
         <f>IF(D42="Bear",60,IF(D42="Base",75,IF(D42="Bull",90,75)))</f>
         <v/>
@@ -19696,15 +19684,9 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="489">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="69" t="inlineStr">
-        <is>
-          <t>Revenue Sensitivity (per $1/bbl Brent)</t>
-        </is>
-      </c>
+      <c r="B43" s="69" t="n"/>
       <c r="C43" s="191" t="n"/>
-      <c r="D43" s="535" t="n">
-        <v>1700</v>
-      </c>
+      <c r="D43" s="535" t="n"/>
       <c r="E43" s="589">
         <f>E18</f>
         <v/>
@@ -19744,15 +19726,9 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="489">
       <c r="A44" s="3" t="n"/>
-      <c r="B44" s="69" t="inlineStr">
-        <is>
-          <t>Brent Reference Price LTM ($/bbl)</t>
-        </is>
-      </c>
+      <c r="B44" s="69" t="n"/>
       <c r="C44" s="191" t="n"/>
-      <c r="D44" s="536" t="n">
-        <v>70</v>
-      </c>
+      <c r="D44" s="536" t="n"/>
       <c r="E44" s="589">
         <f>E18*(-INPUT!E104)</f>
         <v/>
@@ -19792,11 +19768,7 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="489">
       <c r="A45" s="3" t="n"/>
-      <c r="B45" s="504" t="inlineStr">
-        <is>
-          <t>Brent-Adjusted Revenue Growth (Y1-Y5)</t>
-        </is>
-      </c>
+      <c r="B45" s="504" t="n"/>
       <c r="C45" s="191" t="n"/>
       <c r="D45" s="592">
         <f>IFERROR(((INPUT!H9+(E42-D44)*D43)/INPUT!H9)-1,0)</f>
@@ -19841,17 +19813,9 @@
     </row>
     <row r="46" ht="15" customHeight="1" s="489">
       <c r="A46" s="65" t="n"/>
-      <c r="B46" s="48" t="inlineStr">
-        <is>
-          <t>Use Brent Deck? (Yes = Brent-adj. / No = Historical)</t>
-        </is>
-      </c>
+      <c r="B46" s="48" t="n"/>
       <c r="C46" s="82" t="n"/>
-      <c r="D46" s="538" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D46" s="538" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="489">
       <c r="A47" s="65" t="n"/>

--- a/assets/FinSight_IA_Template_REIT_v1.xlsx
+++ b/assets/FinSight_IA_Template_REIT_v1.xlsx
@@ -9,22 +9,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RATIOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOTP" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARABLES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCENARIOS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD 2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STOCK_DATA" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECTOR_REF" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARABLES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCENARIOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STOCK_DATA" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SECTOR_REF" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'INPUT'!$A$1:$H$126</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'RATIOS'!$A$1:$H$72</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'DCF'!$A$1:$L$118</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'COMPARABLES'!$A$1:$L$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'SCENARIOS'!$A$1:$I$54</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'DASHBOARD'!$A$1:$N$95</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'DASHBOARD 2'!$A$1:$P$107</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'COMPARABLES'!$A$1:$L$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'SCENARIOS'!$A$1:$I$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'DASHBOARD'!$A$1:$N$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'DASHBOARD 2'!$A$1:$P$107</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1201,7 +1200,7 @@
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="686">
+  <cellXfs count="674">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2782,42 +2781,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="175" fontId="121" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="115" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="115" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="113" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="115" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="175" fontId="127" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="126" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="126" fillId="9" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="128" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="128" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="126" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="179" fontId="126" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="169" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -10628,81 +10591,6 @@
     <author>Baptiste jeh</author>
   </authors>
   <commentList>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-EBITDA Upstream estimé LTM. Source : TTE Factbook 2024. Ajustable.</t>
-      </text>
-    </comment>
-    <comment ref="E6" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-Peers Upstream pure-play : EOG, PXD, DVN. EV/EBITDA 5-6x. Source : Bloomberg consensus.</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-EBITDA iGRP + LNG estimé LTM. TTE est le 2e plus grand trader LNG au monde. Source : TTE Factbook 2024.</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-Premium LNG/Gas : Shell LNG, Cheniere. EV/EBITDA 7-8x (contrats long-terme, visibilité cash flow). Source : consensus sell-side.</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-EBITDA Renewables &amp; Power estimé LTM. TTE Factbook 2024. Segment en forte croissance (objectif 100GW 2030).</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-Peers Renewables (Enel, Orsted, Iberdrola). EV/EBITDA 10-14x. Prime de croissance ESG.</t>
-      </text>
-    </comment>
-    <comment ref="D9" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-EBITDA Refining &amp; Chemicals estimé LTM. Marges volatiles, cycle bas 2024. Source : TTE Factbook 2024.</t>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-Peers Refining (Valero, MPC, Phillips 66). EV/EBITDA 4-5x (activité cyclique, marges compressées).</t>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-Coûts corporate / overhead non-alloués. Estimé -$2.5B EBITDA. Appliqué à multiple 5x (valeur négative = soustraction).</t>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
-      <text>
-        <t>Net Debt = Short-Term Debt (H48) + Long-Term Debt (H54) - Cash (H34). LTM: $10.2B + $48.0B - $24.2B = ~$34B.</t>
-      </text>
-    </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
-      <text>
-        <t>Baptiste jeh:
-Minorités + instruments hybrides TTE estimés. Source : TTE Annual Report 2024.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Baptiste jeh</author>
-  </authors>
-  <commentList>
     <comment ref="F12" authorId="0" shapeId="0">
       <text>
         <t>Baptiste jeh:
@@ -10719,7 +10607,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Baptiste jeh</author>
@@ -14334,1733 +14222,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="23.109375" bestFit="1" customWidth="1" style="489" min="1" max="1"/>
-    <col width="28.109375" bestFit="1" customWidth="1" style="489" min="2" max="2"/>
-    <col width="11" bestFit="1" customWidth="1" style="489" min="3" max="3"/>
-    <col width="8.44140625" bestFit="1" customWidth="1" style="489" min="4" max="4"/>
-    <col width="10" bestFit="1" customWidth="1" style="489" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="154" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="B1" s="154" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="C1" s="154" t="inlineStr">
-        <is>
-          <t>Pessimiste</t>
-        </is>
-      </c>
-      <c r="D1" s="154" t="inlineStr">
-        <is>
-          <t>Realiste</t>
-        </is>
-      </c>
-      <c r="E1" s="154" t="inlineStr">
-        <is>
-          <t>Optimiste</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="489">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C2" s="285" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D2" s="285" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E2" s="285" t="n">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="489">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C3" s="285" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D3" s="285" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E3" s="285" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="489">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C4" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D4" s="285" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E4" s="285" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="489">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>SG&amp;A (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C5" s="285" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D5" s="285" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E5" s="285" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="489">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>R&amp;D (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C6" s="285" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D6" s="285" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E6" s="285" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="489">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C7" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D7" s="285" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E7" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="489">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C8" s="285" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D8" s="285" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E8" s="285" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="489">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C9" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D9" s="285" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E9" s="285" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="489">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C10" s="285" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D10" s="285" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E10" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="489">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Technologie / SaaS</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C11" s="285" t="n">
-        <v>12</v>
-      </c>
-      <c r="D11" s="285" t="n">
-        <v>16</v>
-      </c>
-      <c r="E11" s="285" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="489">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C12" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D12" s="285" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E12" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="489">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C13" s="285" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D13" s="285" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E13" s="285" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="489">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C14" s="285" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D14" s="285" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E14" s="285" t="n">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="489">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>SG&amp;A (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C15" s="285" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D15" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E15" s="285" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="489">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>R&amp;D (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C16" s="285" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D16" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E16" s="285" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="489">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C17" s="285" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D17" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E17" s="285" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="489">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C18" s="285" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D18" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E18" s="285" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="489">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C19" s="285" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E19" s="285" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="489">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C20" s="285" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D20" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E20" s="285" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="489">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Industrie / Manufacturing</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C21" s="285" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" s="285" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" s="285" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="489">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C22" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D22" s="285" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E22" s="285" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="489">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C23" s="285" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D23" s="285" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E23" s="285" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="489">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C24" s="285" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D24" s="285" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E24" s="285" t="n">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="489">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>SG&amp;A (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C25" s="285" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D25" s="285" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E25" s="285" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="489">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>R&amp;D (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C26" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D26" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E26" s="285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="489">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C27" s="285" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D27" s="285" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E27" s="285" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="489">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C28" s="285" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D28" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E28" s="285" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="489">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C29" s="285" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E29" s="285" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="489">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C30" s="285" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D30" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E30" s="285" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="489">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Consommation / Retail</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C31" s="285" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" s="285" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" s="285" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="489">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C32" s="285" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D32" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E32" s="285" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="489">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C33" s="285" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D33" s="285" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E33" s="285" t="n">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="489">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C34" s="285" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D34" s="285" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E34" s="285" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="489">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>SG&amp;A (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C35" s="285" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D35" s="285" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E35" s="285" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="489">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>R&amp;D (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C36" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D36" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E36" s="285" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="489">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C37" s="285" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D37" s="285" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E37" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="489">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C38" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D38" s="285" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E38" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="489">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C39" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D39" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E39" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="489">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C40" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D40" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E40" s="285" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="489">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Luxe / Premium</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C41" s="285" t="n">
-        <v>12</v>
-      </c>
-      <c r="D41" s="285" t="n">
-        <v>18</v>
-      </c>
-      <c r="E41" s="285" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="489">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C42" s="285" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="D42" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E42" s="285" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="489">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C43" s="285" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D43" s="285" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E43" s="285" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="489">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C44" s="285" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D44" s="285" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E44" s="285" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="489">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>SG&amp;A (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C45" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D45" s="285" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E45" s="285" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="489">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>R&amp;D (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C46" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D46" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E46" s="285" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="489">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C47" s="285" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D47" s="285" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E47" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="489">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C48" s="285" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D48" s="285" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E48" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="489">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C49" s="285" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E49" s="285" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="489">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C50" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D50" s="285" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E50" s="285" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="489">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Energie / Utilities</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C51" s="285" t="n">
-        <v>6</v>
-      </c>
-      <c r="D51" s="285" t="n">
-        <v>8</v>
-      </c>
-      <c r="E51" s="285" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="489">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C52" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D52" s="285" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E52" s="285" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="489">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C53" s="285" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D53" s="285" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E53" s="285" t="n">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="489">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C54" s="285" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D54" s="285" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E54" s="285" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="489">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>SG&amp;A (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C55" s="285" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D55" s="285" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E55" s="285" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="489">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>R&amp;D (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C56" s="285" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D56" s="285" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E56" s="285" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="489">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C57" s="285" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D57" s="285" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E57" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="489">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C58" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D58" s="285" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E58" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="489">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C59" s="285" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D59" s="285" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E59" s="285" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="489">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C60" s="285" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D60" s="285" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E60" s="285" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="489">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Sante / Pharma</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C61" s="285" t="n">
-        <v>8</v>
-      </c>
-      <c r="D61" s="285" t="n">
-        <v>12</v>
-      </c>
-      <c r="E61" s="285" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="489">
-      <c r="A62" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B62" s="68" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C62" s="581" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="D62" s="581" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E62" s="581" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="489">
-      <c r="A63" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B63" s="68" t="inlineStr">
-        <is>
-          <t>Gross Margin (after royalties)</t>
-        </is>
-      </c>
-      <c r="C63" s="581" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D63" s="581" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E63" s="581" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="489">
-      <c r="A64" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B64" s="68" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C64" s="581" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D64" s="581" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E64" s="581" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="489">
-      <c r="A65" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B65" s="68" t="inlineStr">
-        <is>
-          <t>Production Cost (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C65" s="581" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D65" s="581" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E65" s="581" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="489">
-      <c r="A66" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B66" s="68" t="inlineStr">
-        <is>
-          <t>Exploration Expense (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C66" s="581" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D66" s="581" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E66" s="581" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="489">
-      <c r="A67" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B67" s="68" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C67" s="581" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D67" s="581" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E67" s="581" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="489">
-      <c r="A68" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B68" s="68" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C68" s="581" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D68" s="581" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E68" s="581" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="489">
-      <c r="A69" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B69" s="68" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C69" s="581" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D69" s="581" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E69" s="581" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="489">
-      <c r="A70" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B70" s="68" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C70" s="581" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="D70" s="581" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E70" s="581" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="489">
-      <c r="A71" s="68" t="inlineStr">
-        <is>
-          <t>Energie / Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B71" s="68" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C71" s="430" t="n">
-        <v>4</v>
-      </c>
-      <c r="D71" s="430" t="n">
-        <v>6</v>
-      </c>
-      <c r="E71" s="430" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Revenue Growth Rate (Y1-Y5)</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Gross Margin</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>EBITDA Margin</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>SG&amp;A (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>R&amp;D (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>CapEx (% Revenue)</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Change in NWC (% Rev Change)</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.005</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Immobilier / REIT</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>EV/EBITDA Exit Multiple</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>15</v>
-      </c>
-      <c r="D82" t="n">
-        <v>18</v>
-      </c>
-      <c r="E82" t="n">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -21946,526 +20107,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="1.77734375" customWidth="1" style="489" min="1" max="1"/>
-    <col width="43.44140625" customWidth="1" style="489" min="2" max="2"/>
-    <col width="12.6640625" customWidth="1" style="489" min="3" max="3"/>
-    <col width="12.5546875" bestFit="1" customWidth="1" style="489" min="4" max="4"/>
-    <col width="13.88671875" bestFit="1" customWidth="1" style="489" min="5" max="5"/>
-    <col width="15.6640625" bestFit="1" customWidth="1" style="489" min="6" max="6"/>
-    <col width="13.109375" bestFit="1" customWidth="1" style="489" min="7" max="7"/>
-    <col width="20.33203125" customWidth="1" style="489" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26.4" customHeight="1" s="489">
-      <c r="B1" s="434" t="inlineStr">
-        <is>
-          <t>FinSight</t>
-        </is>
-      </c>
-      <c r="C1" s="99" t="n"/>
-      <c r="D1" s="99" t="n"/>
-      <c r="E1" s="99" t="n"/>
-      <c r="F1" s="99" t="n"/>
-      <c r="G1" s="99" t="n"/>
-      <c r="H1" s="99" t="n"/>
-      <c r="I1" s="99" t="n"/>
-      <c r="J1" s="435" t="inlineStr">
-        <is>
-          <t>SOTP — Sum-of-the-Parts Valuation</t>
-        </is>
-      </c>
-      <c r="K1" s="99" t="n"/>
-    </row>
-    <row r="2" ht="21" customHeight="1" s="489">
-      <c r="B2" s="427" t="inlineStr">
-        <is>
-          <t>SOTP</t>
-        </is>
-      </c>
-      <c r="C2" s="124" t="n"/>
-      <c r="D2" s="124" t="n"/>
-      <c r="E2" s="124" t="n"/>
-      <c r="F2" s="124" t="n"/>
-      <c r="G2" s="124" t="n"/>
-      <c r="H2" s="124" t="n"/>
-      <c r="I2" s="124" t="n"/>
-      <c r="J2" s="124" t="n"/>
-      <c r="K2" s="124" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="480" t="inlineStr">
-        <is>
-          <t>All figures in USD millions unless stated | Segments: Upstream / iGRP (LNG+Gas) / Renewables &amp; Power / Refining &amp; Chemicals</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="489">
-      <c r="A4" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B4" s="436" t="inlineStr">
-        <is>
-          <t>SEGMENT OVERVIEW</t>
-        </is>
-      </c>
-      <c r="C4" s="437" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="D4" s="438" t="inlineStr">
-        <is>
-          <t>EBITDA ($M)</t>
-        </is>
-      </c>
-      <c r="E4" s="438" t="inlineStr">
-        <is>
-          <t>EV/EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="F4" s="438" t="inlineStr">
-        <is>
-          <t>Implied EV ($M)</t>
-        </is>
-      </c>
-      <c r="G4" s="438" t="inlineStr">
-        <is>
-          <t>% of Total EV</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="489">
-      <c r="B5" s="539" t="n"/>
-      <c r="C5" s="540" t="n"/>
-      <c r="D5" s="541" t="n"/>
-      <c r="E5" s="541" t="n"/>
-      <c r="F5" s="541" t="n"/>
-      <c r="G5" s="541" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="489">
-      <c r="B6" s="416" t="inlineStr">
-        <is>
-          <t>1. Exploration &amp; Production (Upstream)</t>
-        </is>
-      </c>
-      <c r="C6" s="439" t="inlineStr">
-        <is>
-          <t>Upstream</t>
-        </is>
-      </c>
-      <c r="D6" s="440" t="n">
-        <v>18500</v>
-      </c>
-      <c r="E6" s="614" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F6" s="442">
-        <f>D6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="602">
-        <f>IFERROR(F6/F11,"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="489">
-      <c r="B7" s="416" t="inlineStr">
-        <is>
-          <t>2. Integrated Gas, Renewables &amp; Power (iGRP)</t>
-        </is>
-      </c>
-      <c r="C7" s="439" t="inlineStr">
-        <is>
-          <t>iGRP / LNG</t>
-        </is>
-      </c>
-      <c r="D7" s="440" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E7" s="614" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F7" s="442">
-        <f>D7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="602">
-        <f>IFERROR(F7/F11,"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="489">
-      <c r="B8" s="416" t="inlineStr">
-        <is>
-          <t>3. Renewables &amp; Power (R&amp;P)</t>
-        </is>
-      </c>
-      <c r="C8" s="439" t="inlineStr">
-        <is>
-          <t>Renewables</t>
-        </is>
-      </c>
-      <c r="D8" s="440" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E8" s="614" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" s="442">
-        <f>D8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="602">
-        <f>IFERROR(F8/F11,"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="489">
-      <c r="B9" s="416" t="inlineStr">
-        <is>
-          <t>4. Refining, Chemicals &amp; Marketing (RCM)</t>
-        </is>
-      </c>
-      <c r="C9" s="439" t="inlineStr">
-        <is>
-          <t>Refining</t>
-        </is>
-      </c>
-      <c r="D9" s="440" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E9" s="614" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="442">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="602">
-        <f>IFERROR(F9/F11,"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="489">
-      <c r="B10" s="416" t="inlineStr">
-        <is>
-          <t>5. Corporate / Holding (Overhead &amp; Eliminations)</t>
-        </is>
-      </c>
-      <c r="C10" s="439" t="inlineStr">
-        <is>
-          <t>Corporate</t>
-        </is>
-      </c>
-      <c r="D10" s="440" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="E10" s="614" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="442">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="602">
-        <f>IFERROR(F10/F11,"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15.6" customHeight="1" s="489" thickBot="1">
-      <c r="B11" s="418" t="inlineStr">
-        <is>
-          <t>TOTAL GROSS ASSET VALUE (Sum of Parts)</t>
-        </is>
-      </c>
-      <c r="F11" s="443">
-        <f>SUM(F6:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="615">
-        <f>IFERROR(F11/F11,"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="489">
-      <c r="B13" s="415" t="inlineStr">
-        <is>
-          <t>BRIDGE TO EQUITY VALUE</t>
-        </is>
-      </c>
-      <c r="C13" s="124" t="n"/>
-      <c r="D13" s="124" t="n"/>
-      <c r="E13" s="124" t="n"/>
-      <c r="F13" s="124" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="489">
-      <c r="B14" s="542" t="n"/>
-      <c r="C14" s="392" t="n"/>
-      <c r="D14" s="392" t="n"/>
-      <c r="E14" s="392" t="n"/>
-      <c r="F14" s="392" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="489">
-      <c r="B15" s="416" t="inlineStr">
-        <is>
-          <t>Total Gross Asset Value (Segment EV)</t>
-        </is>
-      </c>
-      <c r="F15" s="442">
-        <f>F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="489">
-      <c r="B16" s="416" t="inlineStr">
-        <is>
-          <t>(-) Net Debt (LTM)</t>
-        </is>
-      </c>
-      <c r="C16" s="417" t="n"/>
-      <c r="F16" s="590">
-        <f>-(INPUT!H48+INPUT!H54-INPUT!H34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="489">
-      <c r="B17" s="416" t="inlineStr">
-        <is>
-          <t>(+) Minorities &amp; Hybrid Adj. (approx.)</t>
-        </is>
-      </c>
-      <c r="C17" s="417" t="n"/>
-      <c r="F17" s="440" t="n">
-        <v>-8000</v>
-      </c>
-    </row>
-    <row r="18" ht="15.6" customHeight="1" s="489" thickBot="1">
-      <c r="B18" s="418" t="inlineStr">
-        <is>
-          <t>IMPLIED EQUITY VALUE (SOTP)</t>
-        </is>
-      </c>
-      <c r="F18" s="443">
-        <f>F15+F16+F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="489">
-      <c r="B20" s="416" t="inlineStr">
-        <is>
-          <t>Shares Outstanding (Diluted, M)</t>
-        </is>
-      </c>
-      <c r="C20" s="417" t="n"/>
-      <c r="F20" s="444">
-        <f>INPUT!H96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="489">
-      <c r="B21" s="418" t="inlineStr">
-        <is>
-          <t>IMPLIED SHARE PRICE (SOTP) ($)</t>
-        </is>
-      </c>
-      <c r="F21" s="616">
-        <f>IFERROR(F18/(F20),"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="489">
-      <c r="B22" s="416" t="inlineStr">
-        <is>
-          <t>Current Share Price ($)</t>
-        </is>
-      </c>
-      <c r="F22" s="617">
-        <f>INPUT!H95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="489">
-      <c r="A23" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="B23" s="418" t="inlineStr">
-        <is>
-          <t>Implied Upside / (Downside)</t>
-        </is>
-      </c>
-      <c r="F23" s="618">
-        <f>IFERROR(F21/F22-1,"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="489">
-      <c r="B25" s="415" t="inlineStr">
-        <is>
-          <t>SENSITIVITY — Implied Share Price ($) vs Upstream EV/EBITDA &amp; LNG EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C25" s="124" t="n"/>
-      <c r="D25" s="124" t="n"/>
-      <c r="E25" s="124" t="n"/>
-      <c r="F25" s="124" t="n"/>
-      <c r="G25" s="124" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="485" t="inlineStr">
-        <is>
-          <t>LNG (iGRP) EV/EBITDA →</t>
-        </is>
-      </c>
-      <c r="C26" s="447" t="n"/>
-      <c r="D26" s="619" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" s="619" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F26" s="619" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="485" t="inlineStr">
-        <is>
-          <t>Upstream (E6) ↓</t>
-        </is>
-      </c>
-      <c r="C27" s="619" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D27" s="620">
-        <f>IFERROR((D6*C27+D7*D26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-      <c r="E27" s="621">
-        <f>IFERROR((D6*C27+D7*E26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-      <c r="F27" s="621">
-        <f>IFERROR((D6*C27+D7*F26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="619" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D28" s="622">
-        <f>IFERROR((D6*C28+D7*D26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-      <c r="E28" s="623">
-        <f>IFERROR((D6*C28+D7*E26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-      <c r="F28" s="623">
-        <f>IFERROR((D6*C28+D7*F26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" s="619" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D29" s="624">
-        <f>IFERROR((D6*C29+D7*D26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-      <c r="E29" s="625">
-        <f>IFERROR((D6*C29+D7*E26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-      <c r="F29" s="625">
-        <f>IFERROR((D6*C29+D7*F26+F8+F9+F10+F16+F17)/(F20),"–")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="489">
-      <c r="B32" s="415" t="inlineStr">
-        <is>
-          <t>METHODOLOGY NOTES</t>
-        </is>
-      </c>
-      <c r="C32" s="124" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="451" t="inlineStr">
-        <is>
-          <t>(1) EBITDA by segment are estimates based on TTE Factbook 2024 &amp; analyst consensus. Update D6:D10 with actual reported segment EBITDA when available.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="451" t="inlineStr">
-        <is>
-          <t>(2) EV/EBITDA multiples sourced from Bloomberg sector comparables (E&amp;P peers, LNG peers, Renewables peers, Refining peers).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="451" t="inlineStr">
-        <is>
-          <t>(3) Net Debt linked to INPUT LTM Balance Sheet (ST Debt + LT Debt - Cash). Minorities adj. ($8B) is an estimate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="451" t="inlineStr">
-        <is>
-          <t>(4) Sensitivity table (rows 27-29): Yellow = base case (Upstream 5.5x / LNG 7.5x). Adjust inputs in D6:E10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="489">
-      <c r="B38" s="452" t="inlineStr">
-        <is>
-          <t>© 2015 to 2024 FinSight</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="489">
-      <c r="B39" s="452" t="inlineStr">
-        <is>
-          <t>This Excel model is for educational purposes only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="489">
-      <c r="B40" s="453" t="inlineStr">
-        <is>
-          <t>https://finsight.com/</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O121"/>
@@ -22625,7 +20266,7 @@
       </c>
       <c r="G7" s="33" t="inlineStr">
         <is>
-          <t>EBITDAX
+          <t>NOI
 (LTM)</t>
         </is>
       </c>
@@ -22720,30 +20361,30 @@
           <t>XOM</t>
         </is>
       </c>
-      <c r="D9" s="626" t="n">
+      <c r="D9" s="614" t="n">
         <v>75.33</v>
       </c>
-      <c r="E9" s="627" t="n">
+      <c r="E9" s="615" t="n">
         <v>173303.61</v>
       </c>
-      <c r="F9" s="627" t="n">
+      <c r="F9" s="615" t="n">
         <v>185019.01</v>
       </c>
-      <c r="G9" s="627" t="n">
+      <c r="G9" s="615" t="n">
         <v>17629</v>
       </c>
-      <c r="H9" s="628">
+      <c r="H9" s="616">
         <f>IFERROR(E9/G9,"–")</f>
         <v/>
       </c>
-      <c r="I9" s="628">
+      <c r="I9" s="616">
         <f>IFERROR(E9/F9,"–")</f>
         <v/>
       </c>
-      <c r="J9" s="626" t="n">
+      <c r="J9" s="614" t="n">
         <v>15.98</v>
       </c>
-      <c r="K9" s="628">
+      <c r="K9" s="616">
         <f>IFERROR(D9/J9,"–")</f>
         <v/>
       </c>
@@ -22760,30 +20401,30 @@
           <t>SHEL.L</t>
         </is>
       </c>
-      <c r="D10" s="626" t="n">
+      <c r="D10" s="614" t="n">
         <v>11.62</v>
       </c>
-      <c r="E10" s="627" t="n">
+      <c r="E10" s="615" t="n">
         <v>183371.55</v>
       </c>
-      <c r="F10" s="627" t="n">
+      <c r="F10" s="615" t="n">
         <v>187267.01</v>
       </c>
-      <c r="G10" s="627" t="n">
+      <c r="G10" s="615" t="n">
         <v>5393</v>
       </c>
-      <c r="H10" s="628">
+      <c r="H10" s="616">
         <f>IFERROR(E10/G10,"–")</f>
         <v/>
       </c>
-      <c r="I10" s="628">
+      <c r="I10" s="616">
         <f>IFERROR(E10/F10,"–")</f>
         <v/>
       </c>
-      <c r="J10" s="626" t="n">
+      <c r="J10" s="614" t="n">
         <v>10.81</v>
       </c>
-      <c r="K10" s="628">
+      <c r="K10" s="616">
         <f>IFERROR(D10/J10,"–")</f>
         <v/>
       </c>
@@ -22800,30 +20441,30 @@
           <t>BP.L</t>
         </is>
       </c>
-      <c r="D11" s="626" t="n">
+      <c r="D11" s="614" t="n">
         <v>525.72</v>
       </c>
-      <c r="E11" s="627" t="n">
+      <c r="E11" s="615" t="n">
         <v>1333326.91</v>
       </c>
-      <c r="F11" s="627" t="n">
+      <c r="F11" s="615" t="n">
         <v>200966</v>
       </c>
-      <c r="G11" s="627" t="n">
+      <c r="G11" s="615" t="n">
         <v>101892</v>
       </c>
-      <c r="H11" s="628">
+      <c r="H11" s="616">
         <f>IFERROR(E11/G11,"–")</f>
         <v/>
       </c>
-      <c r="I11" s="628">
+      <c r="I11" s="616">
         <f>IFERROR(E11/F11,"–")</f>
         <v/>
       </c>
-      <c r="J11" s="626" t="n">
+      <c r="J11" s="614" t="n">
         <v>23.5</v>
       </c>
-      <c r="K11" s="628">
+      <c r="K11" s="616">
         <f>IFERROR(D11/J11,"–")</f>
         <v/>
       </c>
@@ -22840,30 +20481,30 @@
           <t>ENI.MI</t>
         </is>
       </c>
-      <c r="D12" s="626" t="n">
+      <c r="D12" s="614" t="n">
         <v>78.45999999999999</v>
       </c>
-      <c r="E12" s="627" t="n">
+      <c r="E12" s="615" t="n">
         <v>144410</v>
       </c>
-      <c r="F12" s="627" t="n">
+      <c r="F12" s="615" t="n">
         <v>133453</v>
       </c>
-      <c r="G12" s="627" t="n">
+      <c r="G12" s="615" t="n">
         <v>15742</v>
       </c>
-      <c r="H12" s="628">
+      <c r="H12" s="616">
         <f>IFERROR(E12/G12,"–")</f>
         <v/>
       </c>
-      <c r="I12" s="628">
+      <c r="I12" s="616">
         <f>IFERROR(E12/F12,"–")</f>
         <v/>
       </c>
-      <c r="J12" s="626" t="n">
+      <c r="J12" s="614" t="n">
         <v>1.3</v>
       </c>
-      <c r="K12" s="628">
+      <c r="K12" s="616">
         <f>IFERROR(D12/J12,"–")</f>
         <v/>
       </c>
@@ -22880,28 +20521,28 @@
           <t>REP.MC</t>
         </is>
       </c>
-      <c r="D13" s="629" t="n">
+      <c r="D13" s="617" t="n">
         <v>87.8</v>
       </c>
-      <c r="E13" s="630" t="n">
+      <c r="E13" s="618" t="n">
         <v>258704.92</v>
       </c>
-      <c r="F13" s="630" t="n">
+      <c r="F13" s="618" t="n">
         <v>321913</v>
       </c>
-      <c r="G13" s="630" t="n">
+      <c r="G13" s="618" t="n">
         <v>24292</v>
       </c>
-      <c r="H13" s="631">
+      <c r="H13" s="619">
         <f>IFERROR(E13/G13,"–")</f>
         <v/>
       </c>
-      <c r="I13" s="631">
+      <c r="I13" s="619">
         <f>IFERROR(E13/F13,"–")</f>
         <v/>
       </c>
-      <c r="J13" s="629" t="n"/>
-      <c r="K13" s="631">
+      <c r="J13" s="617" t="n"/>
+      <c r="K13" s="619">
         <f>IFERROR(D13/J13,"–")</f>
         <v/>
       </c>
@@ -22927,35 +20568,35 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="632">
+      <c r="D15" s="620">
         <f>IFERROR(AVERAGE(D9:D13),"–")</f>
         <v/>
       </c>
-      <c r="E15" s="632">
+      <c r="E15" s="620">
         <f>IFERROR(AVERAGE(E9:E13),"–")</f>
         <v/>
       </c>
-      <c r="F15" s="632">
+      <c r="F15" s="620">
         <f>IFERROR(AVERAGE(F9:F13),"–")</f>
         <v/>
       </c>
-      <c r="G15" s="632">
+      <c r="G15" s="620">
         <f>IFERROR(AVERAGE(G9:G13),"–")</f>
         <v/>
       </c>
-      <c r="H15" s="633">
+      <c r="H15" s="621">
         <f>IFERROR(AVERAGE(H9:H13),"–")</f>
         <v/>
       </c>
-      <c r="I15" s="633">
+      <c r="I15" s="621">
         <f>IFERROR(AVERAGE(I9:I13),"–")</f>
         <v/>
       </c>
-      <c r="J15" s="634">
+      <c r="J15" s="622">
         <f>IFERROR(AVERAGE(J9:J13),"–")</f>
         <v/>
       </c>
-      <c r="K15" s="633">
+      <c r="K15" s="621">
         <f>IFERROR(AVERAGE(K9:K13),"–")</f>
         <v/>
       </c>
@@ -22968,35 +20609,35 @@
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
-      <c r="D16" s="632">
+      <c r="D16" s="620">
         <f>IFERROR(MEDIAN(D9:D13),"–")</f>
         <v/>
       </c>
-      <c r="E16" s="632">
+      <c r="E16" s="620">
         <f>IFERROR(MEDIAN(E9:E13),"–")</f>
         <v/>
       </c>
-      <c r="F16" s="632">
+      <c r="F16" s="620">
         <f>IFERROR(MEDIAN(F9:F13),"–")</f>
         <v/>
       </c>
-      <c r="G16" s="632">
+      <c r="G16" s="620">
         <f>IFERROR(MEDIAN(G9:G13),"–")</f>
         <v/>
       </c>
-      <c r="H16" s="633">
+      <c r="H16" s="621">
         <f>IFERROR(MEDIAN(H9:H13),"–")</f>
         <v/>
       </c>
-      <c r="I16" s="633">
+      <c r="I16" s="621">
         <f>IFERROR(MEDIAN(I9:I13),"–")</f>
         <v/>
       </c>
-      <c r="J16" s="634">
+      <c r="J16" s="622">
         <f>IFERROR(MEDIAN(J9:J13),"–")</f>
         <v/>
       </c>
-      <c r="K16" s="633">
+      <c r="K16" s="621">
         <f>IFERROR(MEDIAN(K9:K13),"–")</f>
         <v/>
       </c>
@@ -23009,35 +20650,35 @@
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="635">
+      <c r="D17" s="623">
         <f>IFERROR(MAX(D9:D13),"–")</f>
         <v/>
       </c>
-      <c r="E17" s="635">
+      <c r="E17" s="623">
         <f>IFERROR(MAX(E9:E13),"–")</f>
         <v/>
       </c>
-      <c r="F17" s="635">
+      <c r="F17" s="623">
         <f>IFERROR(MAX(F9:F13),"–")</f>
         <v/>
       </c>
-      <c r="G17" s="635">
+      <c r="G17" s="623">
         <f>IFERROR(MAX(G9:G13),"–")</f>
         <v/>
       </c>
-      <c r="H17" s="636">
+      <c r="H17" s="624">
         <f>IFERROR(MAX(H9:H13),"–")</f>
         <v/>
       </c>
-      <c r="I17" s="636">
+      <c r="I17" s="624">
         <f>IFERROR(MAX(I9:I13),"–")</f>
         <v/>
       </c>
-      <c r="J17" s="637">
+      <c r="J17" s="625">
         <f>IFERROR(MAX(J9:J13),"–")</f>
         <v/>
       </c>
-      <c r="K17" s="636">
+      <c r="K17" s="624">
         <f>IFERROR(MAX(K9:K13),"–")</f>
         <v/>
       </c>
@@ -23050,35 +20691,35 @@
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
-      <c r="D18" s="638">
+      <c r="D18" s="626">
         <f>IFERROR(MIN(D9:D13),"–")</f>
         <v/>
       </c>
-      <c r="E18" s="638">
+      <c r="E18" s="626">
         <f>IFERROR(MIN(E9:E13),"–")</f>
         <v/>
       </c>
-      <c r="F18" s="638">
+      <c r="F18" s="626">
         <f>IFERROR(MIN(F9:F13),"–")</f>
         <v/>
       </c>
-      <c r="G18" s="638">
+      <c r="G18" s="626">
         <f>IFERROR(MIN(G9:G13),"–")</f>
         <v/>
       </c>
-      <c r="H18" s="639">
+      <c r="H18" s="627">
         <f>IFERROR(MIN(H9:H13),"–")</f>
         <v/>
       </c>
-      <c r="I18" s="639">
+      <c r="I18" s="627">
         <f>IFERROR(MIN(I9:I13),"–")</f>
         <v/>
       </c>
-      <c r="J18" s="640">
+      <c r="J18" s="628">
         <f>IFERROR(MIN(J9:J13),"–")</f>
         <v/>
       </c>
-      <c r="K18" s="639">
+      <c r="K18" s="627">
         <f>IFERROR(MIN(K9:K13),"–")</f>
         <v/>
       </c>
@@ -23156,7 +20797,7 @@
           <t>($M)</t>
         </is>
       </c>
-      <c r="D22" s="641">
+      <c r="D22" s="629">
         <f>INPUT!H9/1000</f>
         <v/>
       </c>
@@ -23181,7 +20822,7 @@
           <t>($M)</t>
         </is>
       </c>
-      <c r="D23" s="641">
+      <c r="D23" s="629">
         <f>INPUT!H30/1000</f>
         <v/>
       </c>
@@ -23231,7 +20872,7 @@
           <t>($M)</t>
         </is>
       </c>
-      <c r="D25" s="641">
+      <c r="D25" s="629">
         <f>IFERROR((INPUT!H54+INPUT!H55-INPUT!H34)/1000,"–")</f>
         <v/>
       </c>
@@ -23256,7 +20897,7 @@
           <t>(M)</t>
         </is>
       </c>
-      <c r="D26" s="642">
+      <c r="D26" s="630">
         <f>INPUT!H96/1000</f>
         <v/>
       </c>
@@ -23315,19 +20956,19 @@
         </is>
       </c>
       <c r="C29" s="9" t="n"/>
-      <c r="D29" s="643">
+      <c r="D29" s="631">
         <f>IFERROR(D23*H18,"–")</f>
         <v/>
       </c>
-      <c r="E29" s="643">
+      <c r="E29" s="631">
         <f>IFERROR(D23*H15,"–")</f>
         <v/>
       </c>
-      <c r="F29" s="643">
+      <c r="F29" s="631">
         <f>IFERROR(D23*H16,"–")</f>
         <v/>
       </c>
-      <c r="G29" s="643">
+      <c r="G29" s="631">
         <f>IFERROR(D23*H17,"–")</f>
         <v/>
       </c>
@@ -23345,19 +20986,19 @@
         </is>
       </c>
       <c r="C30" s="9" t="n"/>
-      <c r="D30" s="643">
+      <c r="D30" s="631">
         <f>IFERROR(D22*I18,"–")</f>
         <v/>
       </c>
-      <c r="E30" s="643">
+      <c r="E30" s="631">
         <f>IFERROR(D22*I15,"–")</f>
         <v/>
       </c>
-      <c r="F30" s="643">
+      <c r="F30" s="631">
         <f>IFERROR(D22*I16,"–")</f>
         <v/>
       </c>
-      <c r="G30" s="643">
+      <c r="G30" s="631">
         <f>IFERROR(D22*I17,"–")</f>
         <v/>
       </c>
@@ -23375,19 +21016,19 @@
         </is>
       </c>
       <c r="C31" s="9" t="n"/>
-      <c r="D31" s="643">
+      <c r="D31" s="631">
         <f>IFERROR(D24*K18*D26,"–")</f>
         <v/>
       </c>
-      <c r="E31" s="643">
+      <c r="E31" s="631">
         <f>IFERROR(D24*K15*D26,"–")</f>
         <v/>
       </c>
-      <c r="F31" s="643">
+      <c r="F31" s="631">
         <f>IFERROR(D24*K16*D26,"–")</f>
         <v/>
       </c>
-      <c r="G31" s="643">
+      <c r="G31" s="631">
         <f>IFERROR(D24*K17*D26,"–")</f>
         <v/>
       </c>
@@ -23423,19 +21064,19 @@
           <t>($M)</t>
         </is>
       </c>
-      <c r="D33" s="643">
+      <c r="D33" s="631">
         <f>IFERROR(AVERAGE(D29,D30),"–")</f>
         <v/>
       </c>
-      <c r="E33" s="643">
+      <c r="E33" s="631">
         <f>IFERROR(AVERAGE(E29,E30),"–")</f>
         <v/>
       </c>
-      <c r="F33" s="643">
+      <c r="F33" s="631">
         <f>IFERROR(AVERAGE(F29,F30),"–")</f>
         <v/>
       </c>
-      <c r="G33" s="643">
+      <c r="G33" s="631">
         <f>IFERROR(AVERAGE(G29,G30),"–")</f>
         <v/>
       </c>
@@ -23457,19 +21098,19 @@
           <t>($M)</t>
         </is>
       </c>
-      <c r="D34" s="643">
+      <c r="D34" s="631">
         <f>D25</f>
         <v/>
       </c>
-      <c r="E34" s="643">
+      <c r="E34" s="631">
         <f>D25</f>
         <v/>
       </c>
-      <c r="F34" s="643">
+      <c r="F34" s="631">
         <f>D25</f>
         <v/>
       </c>
-      <c r="G34" s="643">
+      <c r="G34" s="631">
         <f>D25</f>
         <v/>
       </c>
@@ -23491,19 +21132,19 @@
           <t>($M)</t>
         </is>
       </c>
-      <c r="D35" s="643">
+      <c r="D35" s="631">
         <f>IFERROR(D33-D34,"–")</f>
         <v/>
       </c>
-      <c r="E35" s="643">
+      <c r="E35" s="631">
         <f>IFERROR(E33-E34,"–")</f>
         <v/>
       </c>
-      <c r="F35" s="643">
+      <c r="F35" s="631">
         <f>IFERROR(F33-F34,"–")</f>
         <v/>
       </c>
-      <c r="G35" s="643">
+      <c r="G35" s="631">
         <f>IFERROR(G33-G34,"–")</f>
         <v/>
       </c>
@@ -23525,19 +21166,19 @@
           <t>($)</t>
         </is>
       </c>
-      <c r="D36" s="644">
+      <c r="D36" s="632">
         <f>IFERROR(D35/D26,"–")</f>
         <v/>
       </c>
-      <c r="E36" s="644">
+      <c r="E36" s="632">
         <f>IFERROR(E35/D26,"–")</f>
         <v/>
       </c>
-      <c r="F36" s="644">
+      <c r="F36" s="632">
         <f>IFERROR(F35/D26,"–")</f>
         <v/>
       </c>
-      <c r="G36" s="644">
+      <c r="G36" s="632">
         <f>IFERROR(G35/D26,"–")</f>
         <v/>
       </c>
@@ -23559,19 +21200,19 @@
           <t>($)</t>
         </is>
       </c>
-      <c r="D37" s="634">
+      <c r="D37" s="622">
         <f>INPUT!H95</f>
         <v/>
       </c>
-      <c r="E37" s="634">
+      <c r="E37" s="622">
         <f>INPUT!H95</f>
         <v/>
       </c>
-      <c r="F37" s="634">
+      <c r="F37" s="622">
         <f>INPUT!H95</f>
         <v/>
       </c>
-      <c r="G37" s="634">
+      <c r="G37" s="622">
         <f>INPUT!H95</f>
         <v/>
       </c>
@@ -23593,19 +21234,19 @@
           <t>(%)</t>
         </is>
       </c>
-      <c r="D38" s="645">
+      <c r="D38" s="633">
         <f>IFERROR(D36/D37-1,"–")</f>
         <v/>
       </c>
-      <c r="E38" s="645">
+      <c r="E38" s="633">
         <f>IFERROR(E36/D37-1,"–")</f>
         <v/>
       </c>
-      <c r="F38" s="645">
+      <c r="F38" s="633">
         <f>IFERROR(F36/D37-1,"–")</f>
         <v/>
       </c>
-      <c r="G38" s="645">
+      <c r="G38" s="633">
         <f>IFERROR(G36/D37-1,"–")</f>
         <v/>
       </c>
@@ -23633,10 +21274,10 @@
       <c r="A40" s="3" t="n"/>
       <c r="B40" s="17" t="n"/>
       <c r="C40" s="9" t="n"/>
-      <c r="D40" s="646" t="n"/>
-      <c r="E40" s="647" t="n"/>
-      <c r="F40" s="647" t="n"/>
-      <c r="G40" s="646" t="n"/>
+      <c r="D40" s="634" t="n"/>
+      <c r="E40" s="635" t="n"/>
+      <c r="F40" s="635" t="n"/>
+      <c r="G40" s="634" t="n"/>
       <c r="H40" s="22" t="n"/>
       <c r="I40" s="22" t="n"/>
       <c r="J40" s="22" t="n"/>
@@ -24220,7 +21861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24443,13 +22084,13 @@
         <f t="array" ref="F8">IFERROR(INDEX(SECTOR_REF!$C$2:$E$71,MATCH(1,(SECTOR_REF!$A$2:$A$71=INPUT!$D$116)*(SECTOR_REF!$B$2:$B$71="Revenue Growth Rate (Y1-Y5)"),0),MATCH("Optimiste",{"Pessimiste","Realiste","Optimiste"},0)),IFERROR(INPUT!H9/INPUT!G9-1,0.09))</f>
         <v/>
       </c>
-      <c r="G8" s="648" t="n"/>
+      <c r="G8" s="636" t="n"/>
       <c r="H8" s="586" t="n"/>
-      <c r="I8" s="649" t="n"/>
-      <c r="J8" s="650" t="n"/>
-      <c r="K8" s="650" t="n"/>
-      <c r="L8" s="650" t="n"/>
-      <c r="M8" s="650" t="n"/>
+      <c r="I8" s="637" t="n"/>
+      <c r="J8" s="638" t="n"/>
+      <c r="K8" s="638" t="n"/>
+      <c r="L8" s="638" t="n"/>
+      <c r="M8" s="638" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="489">
       <c r="A9" s="389" t="n"/>
@@ -24473,11 +22114,11 @@
       </c>
       <c r="G9" s="586" t="n"/>
       <c r="H9" s="586" t="n"/>
-      <c r="I9" s="649" t="n"/>
-      <c r="J9" s="650" t="n"/>
-      <c r="K9" s="650" t="n"/>
-      <c r="L9" s="650" t="n"/>
-      <c r="M9" s="650" t="n"/>
+      <c r="I9" s="637" t="n"/>
+      <c r="J9" s="638" t="n"/>
+      <c r="K9" s="638" t="n"/>
+      <c r="L9" s="638" t="n"/>
+      <c r="M9" s="638" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="489">
       <c r="A10" s="389" t="n"/>
@@ -24501,11 +22142,11 @@
       </c>
       <c r="G10" s="586" t="n"/>
       <c r="H10" s="586" t="n"/>
-      <c r="I10" s="649" t="n"/>
-      <c r="J10" s="650" t="n"/>
-      <c r="K10" s="650" t="n"/>
-      <c r="L10" s="650" t="n"/>
-      <c r="M10" s="650" t="n"/>
+      <c r="I10" s="637" t="n"/>
+      <c r="J10" s="638" t="n"/>
+      <c r="K10" s="638" t="n"/>
+      <c r="L10" s="638" t="n"/>
+      <c r="M10" s="638" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="489">
       <c r="A11" s="389" t="n"/>
@@ -24529,11 +22170,11 @@
       </c>
       <c r="G11" s="586" t="n"/>
       <c r="H11" s="586" t="n"/>
-      <c r="I11" s="649" t="n"/>
-      <c r="J11" s="650" t="n"/>
-      <c r="K11" s="650" t="n"/>
-      <c r="L11" s="650" t="n"/>
-      <c r="M11" s="650" t="n"/>
+      <c r="I11" s="637" t="n"/>
+      <c r="J11" s="638" t="n"/>
+      <c r="K11" s="638" t="n"/>
+      <c r="L11" s="638" t="n"/>
+      <c r="M11" s="638" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="489">
       <c r="A12" s="389" t="n"/>
@@ -24557,11 +22198,11 @@
       </c>
       <c r="G12" s="586" t="n"/>
       <c r="H12" s="586" t="n"/>
-      <c r="I12" s="649" t="n"/>
-      <c r="J12" s="650" t="n"/>
-      <c r="K12" s="650" t="n"/>
-      <c r="L12" s="650" t="n"/>
-      <c r="M12" s="650" t="n"/>
+      <c r="I12" s="637" t="n"/>
+      <c r="J12" s="638" t="n"/>
+      <c r="K12" s="638" t="n"/>
+      <c r="L12" s="638" t="n"/>
+      <c r="M12" s="638" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="489">
       <c r="A13" s="389" t="n"/>
@@ -24615,7 +22256,7 @@
           <t>METRIC</t>
         </is>
       </c>
-      <c r="C15" s="651" t="n"/>
+      <c r="C15" s="639" t="n"/>
       <c r="D15" s="334">
         <f>TEXT(INPUT!D117-3,"0")</f>
         <v/>
@@ -24632,23 +22273,23 @@
         <f>INPUT!D117&amp;" (LTM)"</f>
         <v/>
       </c>
-      <c r="H15" s="651">
+      <c r="H15" s="639">
         <f>TEXT(INPUT!D117+1,"0")&amp;"F"</f>
         <v/>
       </c>
-      <c r="I15" s="651">
+      <c r="I15" s="639">
         <f>TEXT(INPUT!D117+2,"0")&amp;"F"</f>
         <v/>
       </c>
-      <c r="J15" s="651">
+      <c r="J15" s="639">
         <f>TEXT(INPUT!D117+3,"0")&amp;"F"</f>
         <v/>
       </c>
-      <c r="K15" s="651">
+      <c r="K15" s="639">
         <f>TEXT(INPUT!D117+4,"0")&amp;"F"</f>
         <v/>
       </c>
-      <c r="L15" s="651">
+      <c r="L15" s="639">
         <f>TEXT(INPUT!D117+5,"0")&amp;"F"</f>
         <v/>
       </c>
@@ -24892,39 +22533,39 @@
         </is>
       </c>
       <c r="C21" s="193" t="n"/>
-      <c r="D21" s="652">
+      <c r="D21" s="640">
         <f>IFERROR(INPUT!E30/INPUT!E9,"–")</f>
         <v/>
       </c>
-      <c r="E21" s="652">
+      <c r="E21" s="640">
         <f>IFERROR(INPUT!F30/INPUT!F9,"–")</f>
         <v/>
       </c>
-      <c r="F21" s="652">
+      <c r="F21" s="640">
         <f>IFERROR(INPUT!G30/INPUT!G9,"–")</f>
         <v/>
       </c>
-      <c r="G21" s="652">
+      <c r="G21" s="640">
         <f>IFERROR(INPUT!H30/INPUT!H9,"–")</f>
         <v/>
       </c>
-      <c r="H21" s="653">
+      <c r="H21" s="641">
         <f>IFERROR(H18/H16,"–")</f>
         <v/>
       </c>
-      <c r="I21" s="653">
+      <c r="I21" s="641">
         <f>IFERROR(I18/I16,"–")</f>
         <v/>
       </c>
-      <c r="J21" s="653">
+      <c r="J21" s="641">
         <f>IFERROR(J18/J16,"–")</f>
         <v/>
       </c>
-      <c r="K21" s="653">
+      <c r="K21" s="641">
         <f>IFERROR(K18/K16,"–")</f>
         <v/>
       </c>
-      <c r="L21" s="653">
+      <c r="L21" s="641">
         <f>IFERROR(L18/L16,"–")</f>
         <v/>
       </c>
@@ -25121,15 +22762,15 @@
         </is>
       </c>
       <c r="C30" s="11" t="n"/>
-      <c r="D30" s="654">
+      <c r="D30" s="642">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="E30" s="655">
+      <c r="E30" s="643">
         <f>$E$10</f>
         <v/>
       </c>
-      <c r="F30" s="655">
+      <c r="F30" s="643">
         <f>$F$10</f>
         <v/>
       </c>
@@ -25173,15 +22814,15 @@
         </is>
       </c>
       <c r="C32" s="474" t="n"/>
-      <c r="D32" s="655">
+      <c r="D32" s="643">
         <f>"—"</f>
         <v/>
       </c>
-      <c r="E32" s="655">
+      <c r="E32" s="643">
         <f>"—"</f>
         <v/>
       </c>
-      <c r="F32" s="655">
+      <c r="F32" s="643">
         <f>IFERROR(F26/D26-1,"–")</f>
         <v/>
       </c>
@@ -25200,7 +22841,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C33" s="656" t="n"/>
+      <c r="C33" s="644" t="n"/>
       <c r="D33" s="123" t="n"/>
       <c r="E33" s="122" t="n"/>
       <c r="F33" s="122" t="n"/>
@@ -25214,26 +22855,26 @@
     </row>
     <row r="34" ht="15" customHeight="1" s="489">
       <c r="A34" s="389" t="n"/>
-      <c r="B34" s="657">
+      <c r="B34" s="645">
         <f>"▶ SCÉNARIO SÉLECTIONNÉ : "&amp;$D$6</f>
         <v/>
       </c>
-      <c r="C34" s="657" t="n"/>
-      <c r="D34" s="657" t="n"/>
-      <c r="E34" s="657" t="n"/>
-      <c r="F34" s="657" t="n"/>
-      <c r="G34" s="657" t="n"/>
-      <c r="H34" s="657" t="n"/>
-      <c r="I34" s="657" t="n"/>
-      <c r="J34" s="657" t="n"/>
-      <c r="K34" s="657" t="n"/>
-      <c r="L34" s="657" t="n"/>
-      <c r="M34" s="657" t="n"/>
+      <c r="C34" s="645" t="n"/>
+      <c r="D34" s="645" t="n"/>
+      <c r="E34" s="645" t="n"/>
+      <c r="F34" s="645" t="n"/>
+      <c r="G34" s="645" t="n"/>
+      <c r="H34" s="645" t="n"/>
+      <c r="I34" s="645" t="n"/>
+      <c r="J34" s="645" t="n"/>
+      <c r="K34" s="645" t="n"/>
+      <c r="L34" s="645" t="n"/>
+      <c r="M34" s="645" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="489">
       <c r="A35" s="389" t="n"/>
       <c r="B35" s="66" t="n"/>
-      <c r="C35" s="656" t="n"/>
+      <c r="C35" s="644" t="n"/>
       <c r="D35" s="123" t="n"/>
       <c r="E35" s="122" t="n"/>
       <c r="F35" s="122" t="n"/>
@@ -25326,7 +22967,7 @@
         <f>IF(INPUT!H9="",NA(),G38*(1+$D$8))</f>
         <v/>
       </c>
-      <c r="I38" s="658" t="n"/>
+      <c r="I38" s="646" t="n"/>
       <c r="J38" s="30" t="n"/>
       <c r="K38" s="30" t="n"/>
       <c r="L38" s="30" t="n"/>
@@ -25483,7 +23124,7 @@
           <t>Pessimistic</t>
         </is>
       </c>
-      <c r="C44" s="656" t="n"/>
+      <c r="C44" s="644" t="n"/>
       <c r="D44" s="567">
         <f>IF(D38=0,0,D38*$D$10)</f>
         <v/>
@@ -25517,7 +23158,7 @@
           <t>Realistic</t>
         </is>
       </c>
-      <c r="C45" s="656" t="n"/>
+      <c r="C45" s="644" t="n"/>
       <c r="D45" s="567">
         <f>IF(D39=0,0,D39*$E$10)</f>
         <v/>
@@ -25551,7 +23192,7 @@
           <t>Optimistic</t>
         </is>
       </c>
-      <c r="C46" s="656" t="n"/>
+      <c r="C46" s="644" t="n"/>
       <c r="D46" s="567">
         <f>IF(D40=0,0,D40*$F$10)</f>
         <v/>
@@ -25586,16 +23227,16 @@
         </is>
       </c>
       <c r="C47" s="68" t="n"/>
-      <c r="D47" s="659" t="n"/>
-      <c r="E47" s="660">
+      <c r="D47" s="647" t="n"/>
+      <c r="E47" s="648">
         <f>IFERROR(H44/H38,"–")</f>
         <v/>
       </c>
-      <c r="F47" s="660">
+      <c r="F47" s="648">
         <f>IFERROR(H45/H39,"–")</f>
         <v/>
       </c>
-      <c r="G47" s="660">
+      <c r="G47" s="648">
         <f>IFERROR(H46/H40,"–")</f>
         <v/>
       </c>
@@ -25614,7 +23255,7 @@
         </is>
       </c>
       <c r="C48" s="63" t="n"/>
-      <c r="D48" s="661" t="n"/>
+      <c r="D48" s="649" t="n"/>
       <c r="E48" s="517">
         <f>IFERROR("$"&amp;TEXT(DCF!D94*(1+$D$8+$D$10-$E$8-$E$10)*0.8,"#,##0.00"),"–")</f>
         <v/>
@@ -25800,7 +23441,7 @@
           <t>Pessimistic</t>
         </is>
       </c>
-      <c r="C57" s="662">
+      <c r="C57" s="650">
         <f>IF(INPUT!H9="",NA(),INPUT!H9*(1+$D$8))</f>
         <v/>
       </c>
@@ -25808,15 +23449,15 @@
         <f>IF(INPUT!H9="",NA(),C57*(1+$D$8))</f>
         <v/>
       </c>
-      <c r="E57" s="662">
+      <c r="E57" s="650">
         <f>IF(INPUT!H9="",NA(),D57*(1+$D$8))</f>
         <v/>
       </c>
-      <c r="F57" s="662">
+      <c r="F57" s="650">
         <f>IF(INPUT!H9="",NA(),E57*(1+$D$8))</f>
         <v/>
       </c>
-      <c r="G57" s="662">
+      <c r="G57" s="650">
         <f>IF(INPUT!H9="",NA(),F57*(1+$D$8))</f>
         <v/>
       </c>
@@ -25834,7 +23475,7 @@
           <t>Realistic</t>
         </is>
       </c>
-      <c r="C58" s="662">
+      <c r="C58" s="650">
         <f>IF(INPUT!H9="",NA(),INPUT!H9*(1+$E$8))</f>
         <v/>
       </c>
@@ -25842,15 +23483,15 @@
         <f>IF(INPUT!H9="",NA(),C58*(1+$E$8))</f>
         <v/>
       </c>
-      <c r="E58" s="662">
+      <c r="E58" s="650">
         <f>IF(INPUT!H9="",NA(),D58*(1+$E$8))</f>
         <v/>
       </c>
-      <c r="F58" s="662">
+      <c r="F58" s="650">
         <f>IF(INPUT!H9="",NA(),E58*(1+$E$8))</f>
         <v/>
       </c>
-      <c r="G58" s="662">
+      <c r="G58" s="650">
         <f>IF(INPUT!H9="",NA(),F58*(1+$E$8))</f>
         <v/>
       </c>
@@ -25868,7 +23509,7 @@
           <t>Optimistic</t>
         </is>
       </c>
-      <c r="C59" s="662">
+      <c r="C59" s="650">
         <f>IF(INPUT!H9="",NA(),INPUT!H9*(1+$F$8))</f>
         <v/>
       </c>
@@ -25876,15 +23517,15 @@
         <f>IF(INPUT!H9="",NA(),C59*(1+$F$8))</f>
         <v/>
       </c>
-      <c r="E59" s="662">
+      <c r="E59" s="650">
         <f>IF(INPUT!H9="",NA(),D59*(1+$F$8))</f>
         <v/>
       </c>
-      <c r="F59" s="662">
+      <c r="F59" s="650">
         <f>IF(INPUT!H9="",NA(),E59*(1+$F$8))</f>
         <v/>
       </c>
-      <c r="G59" s="662">
+      <c r="G59" s="650">
         <f>IF(INPUT!H9="",NA(),F59*(1+$F$8))</f>
         <v/>
       </c>
@@ -25952,7 +23593,7 @@
           <t>Pessimistic</t>
         </is>
       </c>
-      <c r="C62" s="662">
+      <c r="C62" s="650">
         <f>IF(INPUT!H9="",NA(),INPUT!H9*(1+$D$8)*$D$10)</f>
         <v/>
       </c>
@@ -25960,15 +23601,15 @@
         <f>IF(INPUT!H9="",NA(),C57*(1+$D$8)*$D$10)</f>
         <v/>
       </c>
-      <c r="E62" s="662">
+      <c r="E62" s="650">
         <f>IF(INPUT!H9="",NA(),D57*(1+$D$8)*$D$10)</f>
         <v/>
       </c>
-      <c r="F62" s="662">
+      <c r="F62" s="650">
         <f>IF(INPUT!H9="",NA(),E57*(1+$D$8)*$D$10)</f>
         <v/>
       </c>
-      <c r="G62" s="662">
+      <c r="G62" s="650">
         <f>IF(INPUT!H9="",NA(),F57*(1+$D$8)*$D$10)</f>
         <v/>
       </c>
@@ -25986,7 +23627,7 @@
           <t>Realistic</t>
         </is>
       </c>
-      <c r="C63" s="662">
+      <c r="C63" s="650">
         <f>IF(INPUT!H9="",NA(),INPUT!H9*(1+$E$8)*$E$10)</f>
         <v/>
       </c>
@@ -25994,15 +23635,15 @@
         <f>IF(INPUT!H9="",NA(),C58*(1+$E$8)*$E$10)</f>
         <v/>
       </c>
-      <c r="E63" s="662">
+      <c r="E63" s="650">
         <f>IF(INPUT!H9="",NA(),D58*(1+$E$8)*$E$10)</f>
         <v/>
       </c>
-      <c r="F63" s="662">
+      <c r="F63" s="650">
         <f>IF(INPUT!H9="",NA(),E58*(1+$E$8)*$E$10)</f>
         <v/>
       </c>
-      <c r="G63" s="662">
+      <c r="G63" s="650">
         <f>IF(INPUT!H9="",NA(),F58*(1+$E$8)*$E$10)</f>
         <v/>
       </c>
@@ -26020,7 +23661,7 @@
           <t>Optimistic</t>
         </is>
       </c>
-      <c r="C64" s="662">
+      <c r="C64" s="650">
         <f>IF(INPUT!H9="",NA(),INPUT!H9*(1+$F$8)*$F$10)</f>
         <v/>
       </c>
@@ -26028,15 +23669,15 @@
         <f>IF(INPUT!H9="",NA(),C59*(1+$F$8)*$F$10)</f>
         <v/>
       </c>
-      <c r="E64" s="662">
+      <c r="E64" s="650">
         <f>IF(INPUT!H9="",NA(),D59*(1+$F$8)*$F$10)</f>
         <v/>
       </c>
-      <c r="F64" s="662">
+      <c r="F64" s="650">
         <f>IF(INPUT!H9="",NA(),E59*(1+$F$8)*$F$10)</f>
         <v/>
       </c>
-      <c r="G64" s="662">
+      <c r="G64" s="650">
         <f>IF(INPUT!H9="",NA(),F59*(1+$F$8)*$F$10)</f>
         <v/>
       </c>
@@ -26226,7 +23867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27182,9 +24823,9 @@
       <c r="E45" s="356" t="n"/>
       <c r="F45" s="498" t="n"/>
       <c r="H45" s="151" t="n"/>
-      <c r="I45" s="663" t="n"/>
-      <c r="J45" s="663" t="n"/>
-      <c r="K45" s="663" t="n"/>
+      <c r="I45" s="651" t="n"/>
+      <c r="J45" s="651" t="n"/>
+      <c r="K45" s="651" t="n"/>
       <c r="L45" s="179" t="n"/>
       <c r="P45" s="498" t="n"/>
     </row>
@@ -27236,9 +24877,9 @@
       <c r="E47" s="356" t="n"/>
       <c r="F47" s="498" t="n"/>
       <c r="H47" s="151" t="n"/>
-      <c r="I47" s="663" t="n"/>
-      <c r="J47" s="663" t="n"/>
-      <c r="K47" s="663" t="n"/>
+      <c r="I47" s="651" t="n"/>
+      <c r="J47" s="651" t="n"/>
+      <c r="K47" s="651" t="n"/>
       <c r="L47" s="179" t="n"/>
       <c r="P47" s="498" t="n"/>
     </row>
@@ -27290,9 +24931,9 @@
       <c r="E49" s="356" t="n"/>
       <c r="F49" s="498" t="n"/>
       <c r="H49" s="151" t="n"/>
-      <c r="I49" s="663" t="n"/>
-      <c r="J49" s="663" t="n"/>
-      <c r="K49" s="663" t="n"/>
+      <c r="I49" s="651" t="n"/>
+      <c r="J49" s="651" t="n"/>
+      <c r="K49" s="651" t="n"/>
       <c r="L49" s="179" t="n"/>
       <c r="P49" s="498" t="n"/>
     </row>
@@ -27445,7 +25086,7 @@
           <t>Bmk : 12-18x • Prime si qualité assets</t>
         </is>
       </c>
-      <c r="E55" s="664" t="n"/>
+      <c r="E55" s="652" t="n"/>
       <c r="F55" s="451" t="n"/>
       <c r="G55" s="498" t="n"/>
       <c r="H55" s="498" t="n"/>
@@ -27572,11 +25213,11 @@
       </c>
       <c r="M60" s="498" t="n"/>
       <c r="R60" s="486" t="n"/>
-      <c r="S60" s="665">
+      <c r="S60" s="653">
         <f>INPUT!G9</f>
         <v/>
       </c>
-      <c r="T60" s="665">
+      <c r="T60" s="653">
         <f>INPUT!H9</f>
         <v/>
       </c>
@@ -27616,11 +25257,11 @@
         </is>
       </c>
       <c r="C62" s="486" t="n"/>
-      <c r="D62" s="666">
+      <c r="D62" s="654">
         <f>-ABS(INPUT!G10)</f>
         <v/>
       </c>
-      <c r="E62" s="666">
+      <c r="E62" s="654">
         <f>-ABS(INPUT!H10)</f>
         <v/>
       </c>
@@ -27649,11 +25290,11 @@
         </is>
       </c>
       <c r="C63" s="498" t="n"/>
-      <c r="D63" s="667">
+      <c r="D63" s="655">
         <f>S60+D62</f>
         <v/>
       </c>
-      <c r="E63" s="667">
+      <c r="E63" s="655">
         <f>T60+E62</f>
         <v/>
       </c>
@@ -27721,7 +25362,7 @@
         </is>
       </c>
       <c r="I65" s="498" t="n"/>
-      <c r="J65" s="668">
+      <c r="J65" s="656">
         <f>INPUT!G44</f>
         <v/>
       </c>
@@ -27825,7 +25466,7 @@
         <f>D67+D68</f>
         <v/>
       </c>
-      <c r="E69" s="668">
+      <c r="E69" s="656">
         <f>E67+E68</f>
         <v/>
       </c>
@@ -27887,11 +25528,11 @@
         </is>
       </c>
       <c r="C71" s="498" t="n"/>
-      <c r="D71" s="669">
+      <c r="D71" s="657">
         <f>D69+D70</f>
         <v/>
       </c>
-      <c r="E71" s="669">
+      <c r="E71" s="657">
         <f>E69+E70</f>
         <v/>
       </c>
@@ -27903,11 +25544,11 @@
         </is>
       </c>
       <c r="I71" s="498" t="n"/>
-      <c r="J71" s="669">
+      <c r="J71" s="657">
         <f>INPUT!G60</f>
         <v/>
       </c>
-      <c r="K71" s="669">
+      <c r="K71" s="657">
         <f>INPUT!H60</f>
         <v/>
       </c>
@@ -27924,7 +25565,7 @@
         <f>D67+ABS(D66)</f>
         <v/>
       </c>
-      <c r="E72" s="668">
+      <c r="E72" s="656">
         <f>E67+ABS(E66)</f>
         <v/>
       </c>
@@ -27936,7 +25577,7 @@
         </is>
       </c>
       <c r="I72" s="498" t="n"/>
-      <c r="J72" s="668">
+      <c r="J72" s="656">
         <f>INPUT!G63</f>
         <v/>
       </c>
@@ -27949,8 +25590,8 @@
       <c r="A73" s="498" t="n"/>
       <c r="B73" s="69" t="n"/>
       <c r="C73" s="498" t="n"/>
-      <c r="D73" s="670" t="n"/>
-      <c r="E73" s="670" t="n"/>
+      <c r="D73" s="658" t="n"/>
+      <c r="E73" s="658" t="n"/>
       <c r="F73" s="498" t="n"/>
       <c r="G73" s="498" t="n"/>
       <c r="H73" s="498" t="n"/>
@@ -27962,8 +25603,8 @@
     <row r="74" ht="15" customHeight="1" s="489">
       <c r="B74" s="134" t="n"/>
       <c r="C74" s="498" t="n"/>
-      <c r="D74" s="670" t="n"/>
-      <c r="E74" s="670" t="n"/>
+      <c r="D74" s="658" t="n"/>
+      <c r="E74" s="658" t="n"/>
       <c r="F74" s="92" t="n"/>
       <c r="L74" s="498" t="n"/>
     </row>
@@ -28687,7 +26328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28896,15 +26537,15 @@
           <t>52-Week Trading Range</t>
         </is>
       </c>
-      <c r="I6" s="671">
+      <c r="I6" s="659">
         <f>INPUT!H95*0.75</f>
         <v/>
       </c>
-      <c r="J6" s="672">
+      <c r="J6" s="660">
         <f>K6-I6</f>
         <v/>
       </c>
-      <c r="K6" s="673">
+      <c r="K6" s="661">
         <f>INPUT!H95*1.45</f>
         <v/>
       </c>
@@ -28932,15 +26573,15 @@
           <t>Consensus Research</t>
         </is>
       </c>
-      <c r="I7" s="674">
+      <c r="I7" s="662">
         <f>INPUT!H95*1.1</f>
         <v/>
       </c>
-      <c r="J7" s="675">
+      <c r="J7" s="663">
         <f>K7-I7</f>
         <v/>
       </c>
-      <c r="K7" s="673">
+      <c r="K7" s="661">
         <f>INPUT!H95*1.6</f>
         <v/>
       </c>
@@ -28986,15 +26627,15 @@
       </c>
       <c r="G8" s="128" t="n"/>
       <c r="H8" s="128" t="n"/>
-      <c r="I8" s="674">
+      <c r="I8" s="662">
         <f>INPUT!H95*1.2</f>
         <v/>
       </c>
-      <c r="J8" s="675">
+      <c r="J8" s="663">
         <f>K8-I8</f>
         <v/>
       </c>
-      <c r="K8" s="673">
+      <c r="K8" s="661">
         <f>INPUT!H95*1.75</f>
         <v/>
       </c>
@@ -29041,15 +26682,15 @@
       </c>
       <c r="G9" s="128" t="n"/>
       <c r="H9" s="128" t="n"/>
-      <c r="I9" s="674">
+      <c r="I9" s="662">
         <f>INPUT!H95*1.3</f>
         <v/>
       </c>
-      <c r="J9" s="675">
+      <c r="J9" s="663">
         <f>K9-I9</f>
         <v/>
       </c>
-      <c r="K9" s="673">
+      <c r="K9" s="661">
         <f>INPUT!H95*1.85</f>
         <v/>
       </c>
@@ -29080,15 +26721,15 @@
       </c>
       <c r="G10" s="128" t="n"/>
       <c r="H10" s="128" t="n"/>
-      <c r="I10" s="674">
+      <c r="I10" s="662">
         <f>INPUT!H95*1.15</f>
         <v/>
       </c>
-      <c r="J10" s="675">
+      <c r="J10" s="663">
         <f>K10-I10</f>
         <v/>
       </c>
-      <c r="K10" s="673">
+      <c r="K10" s="661">
         <f>INPUT!H95*1.7</f>
         <v/>
       </c>
@@ -29124,12 +26765,12 @@
       </c>
       <c r="G11" s="128" t="n"/>
       <c r="H11" s="128" t="n"/>
-      <c r="I11" s="676">
+      <c r="I11" s="664">
         <f>INPUT!H95</f>
         <v/>
       </c>
-      <c r="J11" s="677" t="n"/>
-      <c r="K11" s="677" t="n"/>
+      <c r="J11" s="665" t="n"/>
+      <c r="K11" s="665" t="n"/>
       <c r="L11" s="128" t="n"/>
       <c r="M11" s="148" t="inlineStr">
         <is>
@@ -29138,23 +26779,23 @@
       </c>
       <c r="N11" s="125" t="n"/>
       <c r="O11" s="125" t="n"/>
-      <c r="P11" s="678">
+      <c r="P11" s="666">
         <f>INPUT!E9</f>
         <v/>
       </c>
-      <c r="Q11" s="678">
+      <c r="Q11" s="666">
         <f>INPUT!E9</f>
         <v/>
       </c>
-      <c r="R11" s="678">
+      <c r="R11" s="666">
         <f>INPUT!F9</f>
         <v/>
       </c>
-      <c r="S11" s="678">
+      <c r="S11" s="666">
         <f>INPUT!G9</f>
         <v/>
       </c>
-      <c r="T11" s="678">
+      <c r="T11" s="666">
         <f>INPUT!H9</f>
         <v/>
       </c>
@@ -29177,23 +26818,23 @@
       </c>
       <c r="N12" s="125" t="n"/>
       <c r="O12" s="125" t="n"/>
-      <c r="P12" s="678">
+      <c r="P12" s="666">
         <f>ABS(INPUT!E10)</f>
         <v/>
       </c>
-      <c r="Q12" s="678">
+      <c r="Q12" s="666">
         <f>ABS(INPUT!E10)</f>
         <v/>
       </c>
-      <c r="R12" s="678">
+      <c r="R12" s="666">
         <f>ABS(INPUT!F10)</f>
         <v/>
       </c>
-      <c r="S12" s="678">
+      <c r="S12" s="666">
         <f>ABS(INPUT!G10)</f>
         <v/>
       </c>
-      <c r="T12" s="678">
+      <c r="T12" s="666">
         <f>ABS(INPUT!H10)</f>
         <v/>
       </c>
@@ -29211,23 +26852,23 @@
       </c>
       <c r="N13" s="125" t="n"/>
       <c r="O13" s="125" t="n"/>
-      <c r="P13" s="679">
+      <c r="P13" s="667">
         <f>INPUT!E11</f>
         <v/>
       </c>
-      <c r="Q13" s="679">
+      <c r="Q13" s="667">
         <f>INPUT!E11</f>
         <v/>
       </c>
-      <c r="R13" s="679">
+      <c r="R13" s="667">
         <f>INPUT!F11</f>
         <v/>
       </c>
-      <c r="S13" s="679">
+      <c r="S13" s="667">
         <f>INPUT!G11</f>
         <v/>
       </c>
-      <c r="T13" s="679">
+      <c r="T13" s="667">
         <f>INPUT!H11</f>
         <v/>
       </c>
@@ -29256,23 +26897,23 @@
       </c>
       <c r="N14" s="125" t="n"/>
       <c r="O14" s="125" t="n"/>
-      <c r="P14" s="678">
+      <c r="P14" s="666">
         <f>ABS(INPUT!E14)</f>
         <v/>
       </c>
-      <c r="Q14" s="678">
+      <c r="Q14" s="666">
         <f>ABS(INPUT!E14)</f>
         <v/>
       </c>
-      <c r="R14" s="678">
+      <c r="R14" s="666">
         <f>ABS(INPUT!F14)</f>
         <v/>
       </c>
-      <c r="S14" s="678">
+      <c r="S14" s="666">
         <f>ABS(INPUT!G14)</f>
         <v/>
       </c>
-      <c r="T14" s="678">
+      <c r="T14" s="666">
         <f>ABS(INPUT!H14)</f>
         <v/>
       </c>
@@ -29301,23 +26942,23 @@
       </c>
       <c r="N15" s="125" t="n"/>
       <c r="O15" s="125" t="n"/>
-      <c r="P15" s="680">
+      <c r="P15" s="668">
         <f>INPUT!E9</f>
         <v/>
       </c>
-      <c r="Q15" s="680">
+      <c r="Q15" s="668">
         <f>INPUT!E9</f>
         <v/>
       </c>
-      <c r="R15" s="680">
+      <c r="R15" s="668">
         <f>INPUT!F9</f>
         <v/>
       </c>
-      <c r="S15" s="680">
+      <c r="S15" s="668">
         <f>INPUT!G9</f>
         <v/>
       </c>
-      <c r="T15" s="680">
+      <c r="T15" s="668">
         <f>INPUT!H9</f>
         <v/>
       </c>
@@ -29338,11 +26979,11 @@
       <c r="M16" s="125" t="n"/>
       <c r="N16" s="125" t="n"/>
       <c r="O16" s="125" t="n"/>
-      <c r="P16" s="677" t="n"/>
-      <c r="Q16" s="677" t="n"/>
-      <c r="R16" s="677" t="n"/>
-      <c r="S16" s="677" t="n"/>
-      <c r="T16" s="677" t="n"/>
+      <c r="P16" s="665" t="n"/>
+      <c r="Q16" s="665" t="n"/>
+      <c r="R16" s="665" t="n"/>
+      <c r="S16" s="665" t="n"/>
+      <c r="T16" s="665" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="489">
       <c r="A17" s="82" t="n"/>
@@ -29364,23 +27005,23 @@
       </c>
       <c r="N17" s="125" t="n"/>
       <c r="O17" s="125" t="n"/>
-      <c r="P17" s="678">
+      <c r="P17" s="666">
         <f>INPUT!E30</f>
         <v/>
       </c>
-      <c r="Q17" s="678">
+      <c r="Q17" s="666">
         <f>INPUT!E30</f>
         <v/>
       </c>
-      <c r="R17" s="678">
+      <c r="R17" s="666">
         <f>INPUT!F30</f>
         <v/>
       </c>
-      <c r="S17" s="678">
+      <c r="S17" s="666">
         <f>INPUT!G30</f>
         <v/>
       </c>
-      <c r="T17" s="678">
+      <c r="T17" s="666">
         <f>INPUT!H30</f>
         <v/>
       </c>
@@ -29405,23 +27046,23 @@
       </c>
       <c r="N18" s="125" t="n"/>
       <c r="O18" s="125" t="n"/>
-      <c r="P18" s="678">
+      <c r="P18" s="666">
         <f>INPUT!E75</f>
         <v/>
       </c>
-      <c r="Q18" s="678">
+      <c r="Q18" s="666">
         <f>INPUT!E75</f>
         <v/>
       </c>
-      <c r="R18" s="678">
+      <c r="R18" s="666">
         <f>INPUT!F75</f>
         <v/>
       </c>
-      <c r="S18" s="678">
+      <c r="S18" s="666">
         <f>INPUT!G75</f>
         <v/>
       </c>
-      <c r="T18" s="678">
+      <c r="T18" s="666">
         <f>INPUT!H75</f>
         <v/>
       </c>
@@ -29446,23 +27087,23 @@
       </c>
       <c r="N19" s="125" t="n"/>
       <c r="O19" s="125" t="n"/>
-      <c r="P19" s="678">
+      <c r="P19" s="666">
         <f>INPUT!E26</f>
         <v/>
       </c>
-      <c r="Q19" s="678">
+      <c r="Q19" s="666">
         <f>INPUT!E26</f>
         <v/>
       </c>
-      <c r="R19" s="678">
+      <c r="R19" s="666">
         <f>INPUT!F26</f>
         <v/>
       </c>
-      <c r="S19" s="678">
+      <c r="S19" s="666">
         <f>INPUT!G26</f>
         <v/>
       </c>
-      <c r="T19" s="678">
+      <c r="T19" s="666">
         <f>INPUT!H26</f>
         <v/>
       </c>
@@ -30144,8 +27785,8 @@
       <c r="N76" s="128" t="n"/>
       <c r="O76" s="128" t="n"/>
       <c r="P76" s="128" t="n"/>
-      <c r="Q76" s="681" t="n"/>
-      <c r="R76" s="682" t="n"/>
+      <c r="Q76" s="669" t="n"/>
+      <c r="R76" s="670" t="n"/>
       <c r="S76" s="125" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="489">
@@ -30156,7 +27797,7 @@
       <c r="F77" s="157" t="n"/>
       <c r="G77" s="157" t="n"/>
       <c r="H77" s="125" t="n"/>
-      <c r="I77" s="681" t="n"/>
+      <c r="I77" s="669" t="n"/>
       <c r="J77" s="128" t="n"/>
       <c r="K77" s="128" t="n"/>
       <c r="L77" s="128" t="n"/>
@@ -30176,7 +27817,7 @@
       <c r="F78" s="157" t="n"/>
       <c r="G78" s="157" t="n"/>
       <c r="H78" s="125" t="n"/>
-      <c r="I78" s="681" t="n"/>
+      <c r="I78" s="669" t="n"/>
       <c r="J78" s="125" t="n"/>
       <c r="K78" s="125" t="n"/>
       <c r="L78" s="125" t="n"/>
@@ -30200,7 +27841,7 @@
       <c r="E79" s="157" t="n"/>
       <c r="F79" s="157" t="n"/>
       <c r="G79" s="157" t="n"/>
-      <c r="I79" s="681" t="n"/>
+      <c r="I79" s="669" t="n"/>
       <c r="J79" s="125" t="n"/>
       <c r="K79" s="125" t="n"/>
       <c r="L79" s="125" t="n"/>
@@ -30208,7 +27849,7 @@
       <c r="N79" s="125" t="n"/>
       <c r="O79" s="125" t="n"/>
       <c r="P79" s="125" t="n"/>
-      <c r="Q79" s="683" t="n"/>
+      <c r="Q79" s="671" t="n"/>
       <c r="R79" s="169" t="n"/>
       <c r="S79" s="169" t="n"/>
       <c r="T79" s="169" t="n"/>
@@ -30224,7 +27865,7 @@
       <c r="E80" s="157" t="n"/>
       <c r="F80" s="157" t="n"/>
       <c r="G80" s="157" t="n"/>
-      <c r="I80" s="681" t="n"/>
+      <c r="I80" s="669" t="n"/>
       <c r="J80" s="125" t="n"/>
       <c r="K80" s="125" t="n"/>
       <c r="L80" s="125" t="n"/>
@@ -30232,7 +27873,7 @@
       <c r="N80" s="125" t="n"/>
       <c r="O80" s="125" t="n"/>
       <c r="P80" s="125" t="n"/>
-      <c r="Q80" s="683" t="n"/>
+      <c r="Q80" s="671" t="n"/>
       <c r="R80" s="169" t="n"/>
       <c r="S80" s="169" t="n"/>
       <c r="T80" s="169" t="n"/>
@@ -30248,7 +27889,7 @@
       <c r="E81" s="157" t="n"/>
       <c r="F81" s="157" t="n"/>
       <c r="G81" s="157" t="n"/>
-      <c r="I81" s="681" t="n"/>
+      <c r="I81" s="669" t="n"/>
       <c r="J81" s="125" t="n"/>
       <c r="K81" s="125" t="n"/>
       <c r="L81" s="125" t="n"/>
@@ -30256,7 +27897,7 @@
       <c r="N81" s="125" t="n"/>
       <c r="O81" s="125" t="n"/>
       <c r="P81" s="125" t="n"/>
-      <c r="Q81" s="683" t="n"/>
+      <c r="Q81" s="671" t="n"/>
       <c r="R81" s="169" t="n"/>
       <c r="S81" s="169" t="n"/>
       <c r="T81" s="169" t="n"/>
@@ -30280,7 +27921,7 @@
       <c r="N82" s="125" t="n"/>
       <c r="O82" s="125" t="n"/>
       <c r="P82" s="125" t="n"/>
-      <c r="Q82" s="683" t="n"/>
+      <c r="Q82" s="671" t="n"/>
       <c r="R82" s="169" t="n"/>
       <c r="S82" s="169" t="n"/>
       <c r="T82" s="169" t="n"/>
@@ -30320,7 +27961,7 @@
       <c r="D84" s="157" t="n"/>
       <c r="E84" s="157" t="n"/>
       <c r="F84" s="157" t="n"/>
-      <c r="G84" s="681" t="n"/>
+      <c r="G84" s="669" t="n"/>
       <c r="H84" s="157" t="n"/>
       <c r="I84" s="157" t="n"/>
       <c r="J84" s="157" t="n"/>
@@ -30437,7 +28078,7 @@
       <c r="E87" s="157" t="n"/>
       <c r="F87" s="157" t="n"/>
       <c r="G87" s="157" t="n"/>
-      <c r="H87" s="684" t="n"/>
+      <c r="H87" s="672" t="n"/>
       <c r="I87" s="125" t="n"/>
       <c r="J87" s="125" t="n"/>
       <c r="K87" s="125" t="n"/>
@@ -30476,7 +28117,7 @@
       <c r="E88" s="157" t="n"/>
       <c r="F88" s="157" t="n"/>
       <c r="G88" s="157" t="n"/>
-      <c r="H88" s="684" t="n"/>
+      <c r="H88" s="672" t="n"/>
       <c r="I88" s="157" t="n"/>
       <c r="J88" s="157" t="n"/>
       <c r="K88" s="157" t="n"/>
@@ -30515,7 +28156,7 @@
       <c r="E89" s="125" t="n"/>
       <c r="F89" s="125" t="n"/>
       <c r="G89" s="125" t="n"/>
-      <c r="H89" s="684" t="n"/>
+      <c r="H89" s="672" t="n"/>
       <c r="I89" s="168" t="n"/>
       <c r="J89" s="168" t="n"/>
       <c r="K89" s="157" t="n"/>
@@ -31446,7 +29087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31496,7 +29137,7 @@
           <t>May-25</t>
         </is>
       </c>
-      <c r="C3" s="685" t="n">
+      <c r="C3" s="673" t="n">
         <v>48.75</v>
       </c>
     </row>
@@ -31509,7 +29150,7 @@
           <t>Jun-25</t>
         </is>
       </c>
-      <c r="C4" s="685" t="n">
+      <c r="C4" s="673" t="n">
         <v>49.16</v>
       </c>
     </row>
@@ -31522,7 +29163,7 @@
           <t>Jul-25</t>
         </is>
       </c>
-      <c r="C5" s="685" t="n">
+      <c r="C5" s="673" t="n">
         <v>49.87</v>
       </c>
     </row>
@@ -31535,7 +29176,7 @@
           <t>Aug-25</t>
         </is>
       </c>
-      <c r="C6" s="685" t="n">
+      <c r="C6" s="673" t="n">
         <v>51.28</v>
       </c>
     </row>
@@ -31548,7 +29189,7 @@
           <t>Sep-25</t>
         </is>
       </c>
-      <c r="C7" s="685" t="n">
+      <c r="C7" s="673" t="n">
         <v>49.59</v>
       </c>
     </row>
@@ -31561,7 +29202,7 @@
           <t>Oct-25</t>
         </is>
       </c>
-      <c r="C8" s="685" t="n">
+      <c r="C8" s="673" t="n">
         <v>51.72</v>
       </c>
     </row>
@@ -31574,7 +29215,7 @@
           <t>Nov-25</t>
         </is>
       </c>
-      <c r="C9" s="685" t="n">
+      <c r="C9" s="673" t="n">
         <v>55.36</v>
       </c>
     </row>
@@ -31587,7 +29228,7 @@
           <t>Dec-25</t>
         </is>
       </c>
-      <c r="C10" s="685" t="n">
+      <c r="C10" s="673" t="n">
         <v>54.18</v>
       </c>
     </row>
@@ -31600,7 +29241,7 @@
           <t>Jan-26</t>
         </is>
       </c>
-      <c r="C11" s="685" t="n">
+      <c r="C11" s="673" t="n">
         <v>60.51</v>
       </c>
     </row>
@@ -31613,7 +29254,7 @@
           <t>Feb-26</t>
         </is>
       </c>
-      <c r="C12" s="685" t="n">
+      <c r="C12" s="673" t="n">
         <v>66.56999999999999</v>
       </c>
     </row>
@@ -31626,7 +29267,7 @@
           <t>Mar-26</t>
         </is>
       </c>
-      <c r="C13" s="685" t="n">
+      <c r="C13" s="673" t="n">
         <v>80.06</v>
       </c>
     </row>
@@ -31639,7 +29280,7 @@
           <t>Apr-26</t>
         </is>
       </c>
-      <c r="C14" s="685" t="n">
+      <c r="C14" s="673" t="n">
         <v>77.69</v>
       </c>
     </row>
@@ -31647,7 +29288,7 @@
       <c r="A15" s="227" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="685" t="n"/>
+      <c r="C15" s="673" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="156" t="inlineStr">
@@ -31659,4 +29300,1731 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E82"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="23.109375" bestFit="1" customWidth="1" style="489" min="1" max="1"/>
+    <col width="28.109375" bestFit="1" customWidth="1" style="489" min="2" max="2"/>
+    <col width="11" bestFit="1" customWidth="1" style="489" min="3" max="3"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" style="489" min="4" max="4"/>
+    <col width="10" bestFit="1" customWidth="1" style="489" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="154" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B1" s="154" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="C1" s="154" t="inlineStr">
+        <is>
+          <t>Pessimiste</t>
+        </is>
+      </c>
+      <c r="D1" s="154" t="inlineStr">
+        <is>
+          <t>Realiste</t>
+        </is>
+      </c>
+      <c r="E1" s="154" t="inlineStr">
+        <is>
+          <t>Optimiste</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="489">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C2" s="285" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" s="285" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E2" s="285" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="489">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C3" s="285" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D3" s="285" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E3" s="285" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="489">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C4" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D4" s="285" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E4" s="285" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="489">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C5" s="285" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="285" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E5" s="285" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="489">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;D (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C6" s="285" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D6" s="285" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E6" s="285" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="489">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C7" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D7" s="285" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="489">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C8" s="285" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="285" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E8" s="285" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="489">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C9" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D9" s="285" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E9" s="285" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="489">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C10" s="285" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D10" s="285" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E10" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="489">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Technologie / SaaS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C11" s="285" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="285" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" s="285" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="489">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C12" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" s="285" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E12" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="489">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C13" s="285" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D13" s="285" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="285" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="489">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C14" s="285" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D14" s="285" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E14" s="285" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="489">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C15" s="285" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E15" s="285" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="489">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;D (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C16" s="285" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D16" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E16" s="285" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="489">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C17" s="285" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E17" s="285" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="489">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C18" s="285" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D18" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E18" s="285" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="489">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C19" s="285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="285" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="489">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C20" s="285" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D20" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E20" s="285" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="489">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Industrie / Manufacturing</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C21" s="285" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="285" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" s="285" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="489">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C22" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D22" s="285" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E22" s="285" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="489">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C23" s="285" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D23" s="285" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E23" s="285" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="489">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C24" s="285" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D24" s="285" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E24" s="285" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="489">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C25" s="285" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D25" s="285" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E25" s="285" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="489">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;D (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C26" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D26" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="489">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C27" s="285" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D27" s="285" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E27" s="285" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="489">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C28" s="285" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E28" s="285" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="489">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C29" s="285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" s="285" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="489">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C30" s="285" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D30" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E30" s="285" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="489">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Consommation / Retail</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C31" s="285" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="285" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="285" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="489">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C32" s="285" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D32" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E32" s="285" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="489">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C33" s="285" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D33" s="285" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E33" s="285" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="489">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C34" s="285" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D34" s="285" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E34" s="285" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="489">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C35" s="285" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D35" s="285" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E35" s="285" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="489">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;D (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C36" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D36" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" s="285" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="489">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C37" s="285" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D37" s="285" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E37" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="489">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C38" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D38" s="285" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E38" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="489">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C39" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D39" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E39" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="489">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C40" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D40" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E40" s="285" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="489">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Luxe / Premium</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C41" s="285" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" s="285" t="n">
+        <v>18</v>
+      </c>
+      <c r="E41" s="285" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="489">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C42" s="285" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D42" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="285" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="489">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C43" s="285" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D43" s="285" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E43" s="285" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="489">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C44" s="285" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D44" s="285" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E44" s="285" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="489">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C45" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D45" s="285" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E45" s="285" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="489">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;D (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C46" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D46" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" s="285" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="489">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C47" s="285" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D47" s="285" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E47" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="489">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C48" s="285" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D48" s="285" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E48" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="489">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C49" s="285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" s="285" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="489">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C50" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D50" s="285" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E50" s="285" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="489">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Energie / Utilities</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C51" s="285" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" s="285" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="285" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="489">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C52" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D52" s="285" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E52" s="285" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="489">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C53" s="285" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D53" s="285" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E53" s="285" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="489">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C54" s="285" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D54" s="285" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E54" s="285" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="489">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>SG&amp;A (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C55" s="285" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D55" s="285" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E55" s="285" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="489">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;D (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C56" s="285" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D56" s="285" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E56" s="285" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="489">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C57" s="285" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D57" s="285" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E57" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="489">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C58" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D58" s="285" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E58" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="489">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C59" s="285" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D59" s="285" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E59" s="285" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="489">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C60" s="285" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D60" s="285" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E60" s="285" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="489">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Sante / Pharma</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C61" s="285" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="285" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" s="285" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="489">
+      <c r="A62" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B62" s="68" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C62" s="581" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D62" s="581" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E62" s="581" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="489">
+      <c r="A63" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B63" s="68" t="inlineStr">
+        <is>
+          <t>Gross Margin (after royalties)</t>
+        </is>
+      </c>
+      <c r="C63" s="581" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D63" s="581" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E63" s="581" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="489">
+      <c r="A64" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B64" s="68" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C64" s="581" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D64" s="581" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E64" s="581" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="489">
+      <c r="A65" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B65" s="68" t="inlineStr">
+        <is>
+          <t>Production Cost (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C65" s="581" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D65" s="581" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E65" s="581" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="489">
+      <c r="A66" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B66" s="68" t="inlineStr">
+        <is>
+          <t>Exploration Expense (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C66" s="581" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D66" s="581" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" s="581" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="489">
+      <c r="A67" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B67" s="68" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C67" s="581" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D67" s="581" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E67" s="581" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="489">
+      <c r="A68" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B68" s="68" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C68" s="581" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D68" s="581" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E68" s="581" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="489">
+      <c r="A69" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B69" s="68" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C69" s="581" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D69" s="581" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E69" s="581" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="489">
+      <c r="A70" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B70" s="68" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C70" s="581" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D70" s="581" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E70" s="581" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="489">
+      <c r="A71" s="68" t="inlineStr">
+        <is>
+          <t>Energie / Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B71" s="68" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C71" s="430" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" s="430" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" s="430" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Revenue Growth Rate (Y1-Y5)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EBITDA Margin</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SG&amp;A (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>R&amp;D (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CapEx (% Revenue)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Change in NWC (% Rev Change)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Immobilier / REIT</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>15</v>
+      </c>
+      <c r="D82" t="n">
+        <v>18</v>
+      </c>
+      <c r="E82" t="n">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="0" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
 </file>